--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>14965.15</v>
+        <v>14910.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>22.82</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>655.7909728308501</v>
+        <v>655.9656841179059</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1346010095379024</v>
+        <v>0.1348350150930409</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04382120946538125</v>
+        <v>0.04399472063352398</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>73.84040381516097</v>
+        <v>73.93400603721634</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>86.13649614454829</v>
+        <v>86.16457681116489</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>43.05520541136636</v>
+        <v>43.07314895733438</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28235.21504215203</v>
+        <v>28254.50762291031</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.8867311749065012</v>
+        <v>0.8949911551840903</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>83.12952722407478</v>
+        <v>83.14974530403873</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>54515.59352924464</v>
+        <v>54543.3795625934</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>2.642836425244294</v>
+        <v>2.658149815399856</v>
       </c>
     </row>
     <row r="15"/>
@@ -3826,7 +3826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3917,6 +3917,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>14910.1</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.0859375</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.134835015093</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>14910.1</v>
+        <v>15045.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>22.73</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.0859375</v>
+        <v>0.1328125</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>655.9656841179059</v>
+        <v>655.860941586748</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1348350150930409</v>
+        <v>0.1346455278755305</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04399472063352398</v>
+        <v>0.04359197907585004</v>
       </c>
     </row>
     <row r="8">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>91.40625</v>
+        <v>86.71875</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>73.93400603721634</v>
+        <v>73.85821115021221</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>86.16457681116489</v>
+        <v>82.86058834506366</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>43.07314895733438</v>
+        <v>43.05861907749568</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28254.50762291031</v>
+        <v>28240.46645159143</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.8949911551840903</v>
+        <v>0.8770104218611892</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>83.14974530403873</v>
+        <v>83.13337360844584</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>54543.3795625934</v>
+        <v>54523.93269211819</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>2.658149815399856</v>
+        <v>2.623948282844195</v>
       </c>
     </row>
     <row r="15"/>
@@ -3826,7 +3826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3950,6 +3950,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>15045.45</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.134645527876</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>15045.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>22.94</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.1328125</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>655.860941586748</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.1346455278755305</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>86.71875</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>73.85821115021221</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>82.86058834506366</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>43.05861907749568</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>28240.46645159143</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.8770104218611892</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>83.13337360844584</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>54523.93269211819</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>2.623948282844195</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.3855604153458748</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.6995397341765872</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.6423058604000583</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,17 +834,17 @@
       <c r="B19" t="n">
         <v>7</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.2545961209779297</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.6313516348216295</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.6529708196426627</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -842,17 +857,17 @@
       <c r="B20" t="n">
         <v>6</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.432145757920493</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.3327947040781369</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.4582269486734742</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -865,17 +880,17 @@
       <c r="B21" t="n">
         <v>7</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.03411110714727905</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.3006230162839707</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.3492759927048708</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -888,21 +903,20 @@
       <c r="B22" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.7010586745977565</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.7407205559391973</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.4667935158060869</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1038,14 +1052,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>2051.06</v>
       </c>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="19">
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1055,14 +1069,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>2262.35</v>
       </c>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="19">
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1072,16 +1086,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>2616.17</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>263.45</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1091,16 +1105,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>2767.18</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>60.44</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1110,16 +1124,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>2805.76</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>67.97</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1129,16 +1143,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>3200.47</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>101.49</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1148,16 +1162,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>3243.35</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>116.81</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1167,16 +1181,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>3390.51</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>161.95</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1186,16 +1200,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>3825</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>47.29</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1205,16 +1219,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>4407.87</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>53.24</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1224,16 +1238,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>4259.75</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>53.39</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1243,16 +1257,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>4653.26</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>55.6</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1262,16 +1276,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>4912.49</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>59.37</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1281,16 +1295,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>4727.85</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>57.19</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1300,16 +1314,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>4451.97</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>122.11</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1319,16 +1333,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>4747.12</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>81.12</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1338,16 +1352,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>5401.17</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>89.88</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1357,16 +1371,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>5593.53</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>90.36</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1376,16 +1390,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>5981.93</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>96.89</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1395,16 +1409,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>6542.41</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>113.66</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1414,16 +1428,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>6529.07</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>83.18000000000001</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1433,16 +1447,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>6978.61</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>71.25</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1452,16 +1466,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>6382.34</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>45.11</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1471,16 +1485,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>6164.19</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>43.1</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1490,16 +1504,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>6861.3</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>49.4</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1509,16 +1523,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>7113.19</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>51.6</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1528,16 +1542,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>7570.15</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>60.91</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1547,16 +1561,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>8194.42</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>57.95</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1566,16 +1580,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>9459.08</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>52.85</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1585,16 +1599,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>9251.200000000001</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>51.94</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1604,16 +1618,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>10119.44</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>57.09</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1623,16 +1637,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>10428.49</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>58.65</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1642,16 +1656,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>10786.23</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>55.91</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1661,16 +1675,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>12161.95</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>66.61</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1680,16 +1694,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>12355.49</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>67.7</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1699,16 +1713,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>11041.17</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>70.48999999999999</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1718,16 +1732,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>12818.2</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>81.84</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1737,16 +1751,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>12855.38</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>82.38</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1756,16 +1770,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>14295.93</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>95.38</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1775,16 +1789,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>14986.98</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>100.3</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1794,16 +1808,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>15960.82</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>107.59</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1813,16 +1827,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>16287.65</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>119.52</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1832,16 +1846,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>16291.81</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>119.79</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1851,16 +1865,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>16089.22</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>124.84</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1870,16 +1884,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>16606.35</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>148.76</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1889,16 +1903,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>15031.78</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>77.09</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1908,16 +1922,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>12665.56</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>42.39</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1927,16 +1941,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>12666.01</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>33.41</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1946,16 +1960,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>13591.56</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>31.81</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1965,16 +1979,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>14313.21</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>33.52</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1984,16 +1998,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>14783.58</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>33.22</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2003,16 +2017,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>15168.25</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>27.44</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2022,16 +2036,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>15104.22</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>26.18</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2041,16 +2055,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>15195.22</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>27.24</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2060,16 +2074,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>15491.18</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>27.64</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2079,16 +2093,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>15305.2</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>26.95</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2098,16 +2112,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>14365</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>27.8</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2117,16 +2131,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>12816.9</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>22.47</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2136,16 +2150,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>12701.65</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>21.38</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2155,16 +2169,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>11025.8</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>17.23</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2174,16 +2188,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>13901.85</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>21.81</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2193,16 +2207,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>13722.6</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>21.57</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2212,16 +2226,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>14023.9</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>22.85</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2231,16 +2245,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>13977.3</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>22.84</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2250,16 +2264,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>14652.95</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>22.84</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2361,13 +2375,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>1819.47</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>33.59</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2375,12 +2389,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,C2)+1)/2)/COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2388,28 +2402,28 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16" t="n"/>
+      <c r="L2" s="30" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>1640.53</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>29.81</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2417,12 +2431,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,C3)+1)/2)/COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2430,28 +2444,28 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16" t="n"/>
+      <c r="L3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>1692.78</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>27.19</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2459,12 +2473,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,C4)+1)/2)/COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2472,28 +2486,28 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16" t="n"/>
+      <c r="L4" s="30" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>1564.85</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>16.24</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2501,12 +2515,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,C5)+1)/2)/COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2514,28 +2528,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>1542.09</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>17.32</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2543,15 +2557,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,C6)+1)/2)/COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2559,28 +2573,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>1504.88</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>16.48</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2588,15 +2602,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,C7)+1)/2)/COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2604,28 +2618,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>1467.08</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>15.52</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2633,15 +2647,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,C8)+1)/2)/COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2649,28 +2663,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>1362.95</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>13.08</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2678,15 +2692,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,C9)+1)/2)/COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2694,28 +2708,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>1345.7</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>13.56</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2723,15 +2737,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,C10)+1)/2)/COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2739,28 +2753,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>1060.42</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>10.68</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2768,15 +2782,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,C11)+1)/2)/COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2784,28 +2798,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>1187.21</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>15.6</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2813,15 +2827,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,C12)+1)/2)/COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2829,28 +2843,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>1470.75</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>31.22</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2858,15 +2872,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,C13)+1)/2)/COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2874,28 +2888,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>1688.31</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>65.55</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2903,15 +2917,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,C14)+1)/2)/COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2919,42 +2933,42 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>1794.26</v>
       </c>
-      <c r="C15" s="7" t="n"/>
+      <c r="C15" s="25" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,C15)+1)/2)/COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -2962,28 +2976,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>2616.17</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>263.45</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2991,15 +3005,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,C16)+1)/2)/COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3007,28 +3021,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>3200.47</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>101.49</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3036,15 +3050,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,C17)+1)/2)/COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3052,25 +3066,25 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="16" t="n"/>
+      <c r="K17" s="30" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>3825</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>47.29</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3078,15 +3092,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,C18)+1)/2)/COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3094,25 +3108,25 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="16" t="n"/>
+      <c r="K18" s="30" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>4653.26</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>55.6</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3120,15 +3134,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,C19)+1)/2)/COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3136,25 +3150,25 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="16" t="n"/>
+      <c r="K19" s="30" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>4451.97</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>122.11</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3162,15 +3176,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,C20)+1)/2)/COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3178,25 +3192,25 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="16" t="n"/>
+      <c r="K20" s="30" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>5593.53</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>90.36</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3204,15 +3218,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,C21)+1)/2)/COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3220,25 +3234,25 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="16" t="n"/>
+      <c r="K21" s="30" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>6529.07</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>83.18000000000001</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3246,15 +3260,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,C22)+1)/2)/COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3262,25 +3276,25 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="16" t="n"/>
+      <c r="K22" s="30" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>6164.19</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>43.1</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3288,15 +3302,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,C23)+1)/2)/COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3304,25 +3318,25 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="16" t="n"/>
+      <c r="K23" s="30" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>7570.15</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>60.91</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3330,15 +3344,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,C24)+1)/2)/COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3346,25 +3360,25 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="16" t="n"/>
+      <c r="K24" s="30" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>9251.200000000001</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>51.94</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3372,15 +3386,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,C25)+1)/2)/COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3388,22 +3402,22 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="J25" s="30" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>10786.23</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>55.91</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3411,15 +3425,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,C26)+1)/2)/COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3427,22 +3441,22 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="J26" s="30" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>11041.17</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>70.48999999999999</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3450,15 +3464,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,C27)+1)/2)/COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3466,22 +3480,22 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>14295.93</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>95.38</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3489,15 +3503,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,C28)+1)/2)/COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3505,22 +3519,22 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="J28" s="30" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>16287.65</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>119.52</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3528,15 +3542,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,C29)+1)/2)/COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3544,22 +3558,22 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="J29" s="30" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>16606.35</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>148.76</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3567,15 +3581,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,C30)+1)/2)/COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3583,22 +3597,22 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>12666.01</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>33.41</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3606,15 +3620,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,C31)+1)/2)/COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3622,22 +3636,22 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>14783.58</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>33.22</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3645,15 +3659,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,C32)+1)/2)/COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3661,22 +3675,22 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="J32" s="30" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>15195.22</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>27.24</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3684,15 +3698,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,C33)+1)/2)/COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3700,19 +3714,19 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16" t="n"/>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="I33" s="30" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>14365</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>27.8</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3720,15 +3734,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,C34)+1)/2)/COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3736,19 +3750,19 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16" t="n"/>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="I34" s="30" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>11025.8</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>17.23</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3756,15 +3770,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,C35)+1)/2)/COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3772,19 +3786,19 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="I35" s="30" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>14023.9</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>22.85</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3792,15 +3806,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,C36)+1)/2)/COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0"))</f>
         <v/>
       </c>
@@ -3808,10 +3822,10 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16" t="n"/>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="I36" s="30" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3888,30 +3902,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>14965.15</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>22.82</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.0859375</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.134601009538</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -3921,30 +3935,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>14910.1</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>22.73</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.0859375</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.134835015093</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -3954,30 +3968,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>15045.45</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>22.94</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.1328125</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.134645527876</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4097,4 +4111,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Sme Emerge Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15045.45</v>
+        <v>15168.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.94</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>655.860941586748</v>
+        <v>656.0575259515571</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1346455278755305</v>
+        <v>0.1331324044733215</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04359197907585004</v>
+        <v>0.04325259515570934</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>73.85821115021221</v>
+        <v>73.25296178932861</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>82.86058834506366</v>
+        <v>82.67901353679858</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>43.05861907749568</v>
+        <v>42.94259277501429</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28240.46645159143</v>
+        <v>28172.81117392108</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.8770104218611892</v>
+        <v>0.857378580234182</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>83.13337360844584</v>
+        <v>83.00263974649499</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>54523.93269211819</v>
+        <v>54454.50647953388</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.623948282844195</v>
+        <v>2.590079573810337</v>
       </c>
     </row>
     <row r="16">
@@ -3843,7 +3843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4000,6 +4000,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>15168.05</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.133132404473</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15168.05</v>
+        <v>15088.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>656.0575259515571</v>
+        <v>656.0217391304348</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1331324044733215</v>
+        <v>0.1330786621173423</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04325259515570934</v>
+        <v>0.04347826086956522</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>73.25296178932861</v>
+        <v>73.23146484693693</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>82.67901353679858</v>
+        <v>82.67256445408107</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>42.94259277501429</v>
+        <v>42.93847181115781</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28172.81117392108</v>
+        <v>28168.57095315889</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.857378580234182</v>
+        <v>0.8668900787459917</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>83.00263974649499</v>
+        <v>82.99799640693837</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>54454.50647953388</v>
+        <v>54448.48994722129</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.590079573810337</v>
+        <v>2.608608539432103</v>
       </c>
     </row>
     <row r="16">
@@ -3843,7 +3843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4036,6 +4036,39 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>15088.5</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.133078662117</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -4048,7 +4081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E534"/>
+  <dimension ref="A1:E533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4073,7 +4106,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -10463,17 +10496,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Parin Enterprises Ltd.</t>
+          <t>Parth Electricals &amp; Engineering Ltd.</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>PARIN</t>
+          <t>PARTH</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10483,17 +10516,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Parth Electricals &amp; Engineering Ltd.</t>
+          <t>Party Cruisers Ltd.</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>PARTH</t>
+          <t>PARTYCRUS</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -10503,17 +10536,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Party Cruisers Ltd.</t>
+          <t>Patil Automation Ltd.</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>PARTYCRUS</t>
+          <t>PATILAUTOM</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10523,12 +10556,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Patil Automation Ltd.</t>
+          <t>PATTECH FITWELL TUBE COMPONENTS Ltd.</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>PATILAUTOM</t>
+          <t>PATTECH</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -10543,17 +10576,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PATTECH FITWELL TUBE COMPONENTS Ltd.</t>
+          <t>Pelatro Ltd.</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>PATTECH</t>
+          <t>PELATRO</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -10563,17 +10596,17 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Pelatro Ltd.</t>
+          <t>Pentagon Rubber Ltd.</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>PELATRO</t>
+          <t>PENTAGON</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10583,17 +10616,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Pentagon Rubber Ltd.</t>
+          <t>Petro Carbon and Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>PENTAGON</t>
+          <t>PCCL</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -10603,17 +10636,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Petro Carbon and Chemicals Ltd.</t>
+          <t>Phantom Digital Effects Ltd.</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>PCCL</t>
+          <t>PHANTOMFX</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -10623,17 +10656,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Phantom Digital Effects Ltd.</t>
+          <t>Phoenix Overseas Ltd.</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>PHANTOMFX</t>
+          <t>PHOGLOBAL</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10643,17 +10676,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Phoenix Overseas Ltd.</t>
+          <t>Picturepost Studios Ltd.</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>PHOGLOBAL</t>
+          <t>PPSL</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -10663,17 +10696,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Picturepost Studios Ltd.</t>
+          <t>Plada Infotech Services Ltd.</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>PPSL</t>
+          <t>PLADAINFO</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10683,17 +10716,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Plada Infotech Services Ltd.</t>
+          <t>Polysil Irrigation Systems Ltd.</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>PLADAINFO</t>
+          <t>POLYSIL</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10703,17 +10736,17 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Polysil Irrigation Systems Ltd.</t>
+          <t>Positron Energy Ltd.</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>POLYSIL</t>
+          <t>POSITRON</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10723,17 +10756,17 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Positron Energy Ltd.</t>
+          <t>Pramara Promotions Ltd.</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>POSITRON</t>
+          <t>PRAMARA</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -10743,17 +10776,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Pramara Promotions Ltd.</t>
+          <t>Pranik Logistics Ltd.</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>PRAMARA</t>
+          <t>PRANIK</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10763,17 +10796,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Pranik Logistics Ltd.</t>
+          <t>Pratham EPC Projects Ltd.</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>PRANIK</t>
+          <t>PRATHAM</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -10783,17 +10816,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Pratham EPC Projects Ltd.</t>
+          <t>Precision Metaliks Ltd.</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>PRATHAM</t>
+          <t>PRECISION</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -10803,17 +10836,17 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Precision Metaliks Ltd.</t>
+          <t>Premier Roadlines Ltd.</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>PRECISION</t>
+          <t>PRLIND</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10823,17 +10856,17 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Premier Roadlines Ltd.</t>
+          <t>Premium Plast Ltd.</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>PRLIND</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -10843,17 +10876,17 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Premium Plast Ltd.</t>
+          <t>Presstonic Engineering Ltd.</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>PRESSTONIC</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10863,12 +10896,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Presstonic Engineering Ltd.</t>
+          <t>Prime Cable Industries Ltd.</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>PRESSTONIC</t>
+          <t>PRIMECAB</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -10883,17 +10916,17 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Prime Cable Industries Ltd.</t>
+          <t>Pritika Engineering Components Ltd.</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>PRIMECAB</t>
+          <t>PRITIKA</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -10903,17 +10936,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Pritika Engineering Components Ltd.</t>
+          <t>Prizor Viztech Ltd.</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>PRITIKA</t>
+          <t>PRIZOR</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10956,17 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Prizor Viztech Ltd.</t>
+          <t>Pro FX Tech Ltd.</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>PRIZOR</t>
+          <t>PROFX</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -10943,17 +10976,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Pro FX Tech Ltd.</t>
+          <t>Prolife Industries Ltd.</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>PROFX</t>
+          <t>PROLIFE</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -10963,17 +10996,17 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Prolife Industries Ltd.</t>
+          <t>Proventus Agrocom Ltd.</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>PROLIFE</t>
+          <t>PROV</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -10983,17 +11016,17 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Proventus Agrocom Ltd.</t>
+          <t>Pulz Electronics Ltd.</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>PROV</t>
+          <t>PULZ</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -11003,17 +11036,17 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Pulz Electronics Ltd.</t>
+          <t>Purple United Sales Ltd.</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>PULZ</t>
+          <t>PURPLEUTED</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -11023,17 +11056,17 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Purple United Sales Ltd.</t>
+          <t>Purv Flexipack Ltd.</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>PURPLEUTED</t>
+          <t>PURVFLEXI</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11043,17 +11076,17 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Purv Flexipack Ltd.</t>
+          <t>Pushpa Jewellers Ltd.</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>PURVFLEXI</t>
+          <t>PUSHPA</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -11063,17 +11096,17 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Pushpa Jewellers Ltd.</t>
+          <t>QUADPRO ITES Ltd.</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>PUSHPA</t>
+          <t>QUADPRO</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11083,17 +11116,17 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>QUADPRO ITES Ltd.</t>
+          <t>Quality Foils (India) Ltd.</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>QUADPRO</t>
+          <t>QFIL</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11103,17 +11136,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Quality Foils (India) Ltd.</t>
+          <t>Quest Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>QFIL</t>
+          <t>QUESTLAB</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11123,17 +11156,17 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Quest Laboratories Ltd.</t>
+          <t>Quicktouch Technologies Ltd.</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>QUESTLAB</t>
+          <t>QUICKTOUCH</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11143,17 +11176,17 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Quicktouch Technologies Ltd.</t>
+          <t>QVC Exports Ltd.</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>QUICKTOUCH</t>
+          <t>QVCEL</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -11163,17 +11196,17 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>QVC Exports Ltd.</t>
+          <t>Rachana Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>QVCEL</t>
+          <t>RILINFRA</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -11183,17 +11216,17 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Rachana Infrastructure Ltd.</t>
+          <t>Radiowalla Network Ltd.</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>RILINFRA</t>
+          <t>RADIOWALLA</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -11203,17 +11236,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Radiowalla Network Ltd.</t>
+          <t>Rajgor Castor Derivatives Ltd.</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>RADIOWALLA</t>
+          <t>RCDL</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -11223,17 +11256,17 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Rajgor Castor Derivatives Ltd.</t>
+          <t>Rajputana Biodiesel Ltd.</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>RCDL</t>
+          <t>RAJPUTANA</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -11243,17 +11276,17 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Rajputana Biodiesel Ltd.</t>
+          <t>Rajputana Industries Ltd.</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>RAJPUTANA</t>
+          <t>RAJINDLTD</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11296,17 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Rajputana Industries Ltd.</t>
+          <t>Rama Telecom Ltd.</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>RAJINDLTD</t>
+          <t>RTL</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -11283,17 +11316,17 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Rama Telecom Ltd.</t>
+          <t>Ramdevbaba Solvent Ltd.</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>RTL</t>
+          <t>RBS</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -11303,17 +11336,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Ramdevbaba Solvent Ltd.</t>
+          <t>Rapid Fleet Management Services Ltd.</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>RBS</t>
+          <t>RAPIDFLEET</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11323,17 +11356,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Rapid Fleet Management Services Ltd.</t>
+          <t>Rappid Valves (India) Ltd.</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>RAPIDFLEET</t>
+          <t>RAPPID</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11343,17 +11376,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Rappid Valves (India) Ltd.</t>
+          <t>RBM Infracon Ltd.</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>RAPPID</t>
+          <t>RBMINFRA</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -11363,17 +11396,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>RBM Infracon Ltd.</t>
+          <t>Readymix Construction Machinery Ltd.</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>RBMINFRA</t>
+          <t>READYMIX</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11383,12 +11416,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Readymix Construction Machinery Ltd.</t>
+          <t>Refractory Shapes Ltd.</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>READYMIX</t>
+          <t>REFRACTORY</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -11403,17 +11436,17 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Refractory Shapes Ltd.</t>
+          <t>Remus Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>REFRACTORY</t>
+          <t>REMUS</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11423,17 +11456,17 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Remus Pharmaceuticals Ltd.</t>
+          <t>Renol Polychem Ltd.</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>REMUS</t>
+          <t>RNPL</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11443,17 +11476,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Renol Polychem Ltd.</t>
+          <t>Rex Pipes and Cables Industries Ltd.</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>RNPL</t>
+          <t>REXPIPES</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11463,17 +11496,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Rex Pipes and Cables Industries Ltd.</t>
+          <t>Rexpro Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>REXPIPES</t>
+          <t>REXPRO</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -11483,17 +11516,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Rexpro Enterprises Ltd.</t>
+          <t>Richa Info Systems Ltd.</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>REXPRO</t>
+          <t>RICHA</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11503,17 +11536,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Richa Info Systems Ltd.</t>
+          <t>Rite Zone Chemcon India Ltd.</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>RICHA</t>
+          <t>RITEZONE</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11523,17 +11556,17 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Rite Zone Chemcon India Ltd.</t>
+          <t>RNFI Services Ltd.</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>RITEZONE</t>
+          <t>RNFI</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11543,17 +11576,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>RNFI Services Ltd.</t>
+          <t>Rockingdeals Circular Economy Ltd.</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>RNFI</t>
+          <t>ROCKINGDCE</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11563,17 +11596,17 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Rockingdeals Circular Economy Ltd.</t>
+          <t>Rox Hi-Tech Ltd.</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>ROCKINGDCE</t>
+          <t>ROXHITECH</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11616,17 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Rox Hi-Tech Ltd.</t>
+          <t>Royal Arc Electrodes Ltd.</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>ROXHITECH</t>
+          <t>ROYALARC</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11603,17 +11636,17 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Royal Arc Electrodes Ltd.</t>
+          <t>Rulka Electricals Ltd.</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>ROYALARC</t>
+          <t>RULKA</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11623,17 +11656,17 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Rulka Electricals Ltd.</t>
+          <t>S A Tech Software India Ltd.</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>RULKA</t>
+          <t>SATECH</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11643,17 +11676,17 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>S A Tech Software India Ltd.</t>
+          <t>S D Retail Ltd.</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>SATECH</t>
+          <t>SDREAMS</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -11663,17 +11696,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>S D Retail Ltd.</t>
+          <t>S J Logistics (India) Ltd.</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>SDREAMS</t>
+          <t>SJLOGISTIC</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11683,17 +11716,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>S J Logistics (India) Ltd.</t>
+          <t>Saakshi Medtech and Panels Ltd.</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>SJLOGISTIC</t>
+          <t>SAAKSHI</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11703,12 +11736,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Saakshi Medtech and Panels Ltd.</t>
+          <t>Sabar Flex India Ltd.</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>SAAKSHI</t>
+          <t>SABAR</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -11723,17 +11756,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Sabar Flex India Ltd.</t>
+          <t>Sacheerome Ltd.</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>SABAR</t>
+          <t>SACHEEROME</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11776,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Sacheerome Ltd.</t>
+          <t>Sadhav Shipping Ltd.</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>SACHEEROME</t>
+          <t>SADHAV</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11763,17 +11796,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Sadhav Shipping Ltd.</t>
+          <t>Safe Enterprises Retail Fixtures Ltd.</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>SADHAV</t>
+          <t>SAFEENTP</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -11783,17 +11816,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Safe Enterprises Retail Fixtures Ltd.</t>
+          <t>Sahaj Solar Ltd.</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>SAFEENTP</t>
+          <t>SAHAJSOLAR</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11803,17 +11836,17 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Sahaj Solar Ltd.</t>
+          <t>Sahana System Ltd.</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>SAHAJSOLAR</t>
+          <t>SAHANA</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11823,17 +11856,17 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Sahana System Ltd.</t>
+          <t>Sahasra Electronic Solutions Ltd.</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>SAHANA</t>
+          <t>SAHASRA</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11843,17 +11876,17 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Sahasra Electronic Solutions Ltd.</t>
+          <t>Saj Hotels Ltd.</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>SAHASRA</t>
+          <t>SAJHOTELS</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -11863,17 +11896,17 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Saj Hotels Ltd.</t>
+          <t>Samay Project Services Ltd.</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>SAJHOTELS</t>
+          <t>SAMAY</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -11883,17 +11916,17 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Samay Project Services Ltd.</t>
+          <t>Sameera Agro And Infra Ltd.</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>SAMAY</t>
+          <t>SAIFL</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11936,17 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Sameera Agro And Infra Ltd.</t>
+          <t>Sangani Hospitals Ltd.</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>SAIFL</t>
+          <t>SANGANI</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11923,17 +11956,17 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Sangani Hospitals Ltd.</t>
+          <t>Sar Televenture Ltd.</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>SANGANI</t>
+          <t>SARTELE</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -11943,17 +11976,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Sar Televenture Ltd.</t>
+          <t>Saroja Pharma Industries India Ltd.</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>SARTELE</t>
+          <t>SAROJA</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11963,17 +11996,17 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Saroja Pharma Industries India Ltd.</t>
+          <t>Sat Kartar Life Ltd.</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>SAROJA</t>
+          <t>SATKARTAR</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11983,17 +12016,17 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Sat Kartar Life Ltd.</t>
+          <t>Sathlokhar Synergys E&amp;C Global Ltd.</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>SATKARTAR</t>
+          <t>SSEGL</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -12003,17 +12036,17 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Sathlokhar Synergys E&amp;C Global Ltd.</t>
+          <t>Sati Poly Plast Ltd.</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>SSEGL</t>
+          <t>SATIPOLY</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12023,17 +12056,17 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Sati Poly Plast Ltd.</t>
+          <t>Sattva Engineering Construction Ltd.</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>SATIPOLY</t>
+          <t>SATTVAENGG</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -12043,17 +12076,17 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Sattva Engineering Construction Ltd.</t>
+          <t>Savy Infra and Logistics Ltd.</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>SATTVAENGG</t>
+          <t>SAVY</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12096,17 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Savy Infra and Logistics Ltd.</t>
+          <t>Sawaliya Food Products Ltd.</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>SAVY</t>
+          <t>SAWALIYA</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12083,17 +12116,17 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Sawaliya Food Products Ltd.</t>
+          <t>Sellowrap Industries Ltd.</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>SAWALIYA</t>
+          <t>SELLOWRAP</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -12103,17 +12136,17 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Sellowrap Industries Ltd.</t>
+          <t>Service Care Ltd.</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>SELLOWRAP</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12123,12 +12156,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Service Care Ltd.</t>
+          <t>Shanthala FMCG Products Ltd.</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>SERVICE</t>
+          <t>SHANTHALA</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -12143,17 +12176,17 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Shanthala FMCG Products Ltd.</t>
+          <t>Sharp Chucks and Machines Ltd.</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>SHANTHALA</t>
+          <t>SCML</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12163,17 +12196,17 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Sharp Chucks and Machines Ltd.</t>
+          <t>Sheel Biotech Ltd.</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>SCML</t>
+          <t>SHEEL</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12183,17 +12216,17 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Sheel Biotech Ltd.</t>
+          <t>Sheetal Universal Ltd.</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SHEEL</t>
+          <t>SHEETAL</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12203,17 +12236,17 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Sheetal Universal Ltd.</t>
+          <t>Shera Energy Ltd.</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>SHEETAL</t>
+          <t>SHERA</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12223,17 +12256,17 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Shera Energy Ltd.</t>
+          <t>Shigan Quantum Technologies Ltd.</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>SHERA</t>
+          <t>SHIGAN</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -12243,17 +12276,17 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Shigan Quantum Technologies Ltd.</t>
+          <t>Shivalic Power Control Ltd.</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>SHIGAN</t>
+          <t>SPCL</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12263,17 +12296,17 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Shivalic Power Control Ltd.</t>
+          <t>Shivashrit Foods Ltd.</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>SPCL</t>
+          <t>SHIVASHRIT</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12283,17 +12316,17 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Shivashrit Foods Ltd.</t>
+          <t>Shree Karni Fabcom Ltd.</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>SHIVASHRIT</t>
+          <t>SHREEKARNI</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -12303,17 +12336,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Shree Karni Fabcom Ltd.</t>
+          <t>Shree OSFM E-Mobility Ltd.</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>SHREEKARNI</t>
+          <t>SHREEOSFM</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12323,17 +12356,17 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Shree OSFM E-Mobility Ltd.</t>
+          <t>Shree Tirupati Balajee FIBC Ltd.</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>SHREEOSFM</t>
+          <t>TIRUPATI</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12343,17 +12376,17 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Shree Tirupati Balajee FIBC Ltd.</t>
+          <t>Shreeji Global FMCG Ltd.</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>TIRUPATI</t>
+          <t>SHETHJI</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12363,12 +12396,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Shreeji Global FMCG Ltd.</t>
+          <t>Shri Ahimsa Naturals Ltd.</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>SHETHJI</t>
+          <t>SHRIAHIMSA</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -12383,17 +12416,17 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Shri Ahimsa Naturals Ltd.</t>
+          <t>Shri Hare-Krishna Sponge Iron Ltd.</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>SHRIAHIMSA</t>
+          <t>SHKSIL</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -12403,17 +12436,17 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Shri Hare-Krishna Sponge Iron Ltd.</t>
+          <t>Shri Kanha Stainless Ltd.</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>SHKSIL</t>
+          <t>SHRIKANHA</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12423,12 +12456,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Shri Kanha Stainless Ltd.</t>
+          <t>Shri Techtex Ltd.</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>SHRIKANHA</t>
+          <t>SHRITECH</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -12443,17 +12476,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Shri Techtex Ltd.</t>
+          <t>Shubhlaxmi Jewel Art Ltd.</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>SHRITECH</t>
+          <t>SHUBHLAXMI</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -12463,17 +12496,17 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Shubhlaxmi Jewel Art Ltd.</t>
+          <t>Shubhshree Biofuels Energy Ltd.</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>SHUBHLAXMI</t>
+          <t>SHUBHSHREE</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12483,17 +12516,17 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Shubhshree Biofuels Energy Ltd.</t>
+          <t>Shyam Dhani Industries Ltd.</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>SHUBHSHREE</t>
+          <t>SHYAMDHANI</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12503,17 +12536,17 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Shyam Dhani Industries Ltd.</t>
+          <t>Siddhi Cotspin Ltd.</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>SHYAMDHANI</t>
+          <t>SIDDHICOTS</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -12523,17 +12556,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Siddhi Cotspin Ltd.</t>
+          <t>Siddhika Coatings Ltd.</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>SIDDHICOTS</t>
+          <t>SIDDHIKA</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -12543,17 +12576,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Siddhika Coatings Ltd.</t>
+          <t>Signoria Creation Ltd.</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>SIDDHIKA</t>
+          <t>SIGNORIA</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -12563,17 +12596,17 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Signoria Creation Ltd.</t>
+          <t>Silkflex Polymers (India) Ltd.</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>SIGNORIA</t>
+          <t>SILKFLEX</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -12583,17 +12616,17 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Silkflex Polymers (India) Ltd.</t>
+          <t>Silky Overseas Ltd.</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>SILKFLEX</t>
+          <t>SILKY</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -12603,17 +12636,17 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Silky Overseas Ltd.</t>
+          <t>Simca Advertising Ltd.</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>SILKY</t>
+          <t>SIMCA</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -12623,17 +12656,17 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Simca Advertising Ltd.</t>
+          <t>SKP Bearing Industries Ltd.</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>SIMCA</t>
+          <t>SKP</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12643,17 +12676,17 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>SKP Bearing Industries Ltd.</t>
+          <t>Slone Infosystems Ltd.</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>SKP</t>
+          <t>SLONE</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -12663,17 +12696,17 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Slone Infosystems Ltd.</t>
+          <t>Smarten Power Systems Ltd.</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>SLONE</t>
+          <t>SMARTEN</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12683,12 +12716,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Smarten Power Systems Ltd.</t>
+          <t>SMVD Poly Pack Ltd.</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>SMARTEN</t>
+          <t>SMVD</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -12703,17 +12736,17 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>SMVD Poly Pack Ltd.</t>
+          <t>Snehaa Organics Ltd.</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SMVD</t>
+          <t>SNEHAA</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -12723,17 +12756,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Snehaa Organics Ltd.</t>
+          <t>Solve Plastic Products Ltd.</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>SNEHAA</t>
+          <t>BALCO</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12743,12 +12776,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Solve Plastic Products Ltd.</t>
+          <t>Sona Machinery Ltd.</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>BALCO</t>
+          <t>SONAMAC</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -12763,17 +12796,17 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Sona Machinery Ltd.</t>
+          <t>Sonu Infratech Ltd.</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>SONAMAC</t>
+          <t>SONUINFRA</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -12783,17 +12816,17 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Sonu Infratech Ltd.</t>
+          <t>Sotac Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>SONUINFRA</t>
+          <t>SOTAC</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -12803,17 +12836,17 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Sotac Pharmaceuticals Ltd.</t>
+          <t>Sp Refractories Ltd.</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>SOTAC</t>
+          <t>SPRL</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12823,17 +12856,17 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Sp Refractories Ltd.</t>
+          <t>Speb Adhesives Ltd.</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>SPRL</t>
+          <t>SPEB</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -12843,17 +12876,17 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Speb Adhesives Ltd.</t>
+          <t>Spectrum Talent Management Ltd.</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>SPEB</t>
+          <t>SPECTSTM</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12863,17 +12896,17 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Spectrum Talent Management Ltd.</t>
+          <t>SPP Polymer Ltd.</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>SPECTSTM</t>
+          <t>SPPPOLY</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12883,17 +12916,17 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>SPP Polymer Ltd.</t>
+          <t>Spunweb Nonwoven Ltd.</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>SPPPOLY</t>
+          <t>SPUNWEB</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -12903,17 +12936,17 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Spunweb Nonwoven Ltd.</t>
+          <t>Srinibas Pradhan Constructions Ltd.</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>SPUNWEB</t>
+          <t>SPCON</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -12923,17 +12956,17 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Srinibas Pradhan Constructions Ltd.</t>
+          <t>Srivari Spices And Foods Ltd.</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>SPCON</t>
+          <t>SSFL</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12943,17 +12976,17 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Srivari Spices And Foods Ltd.</t>
+          <t>Srivasavi Adhesive Tapes Ltd.</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>SSFL</t>
+          <t>SRIVASAVI</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12963,17 +12996,17 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Srivasavi Adhesive Tapes Ltd.</t>
+          <t>Striders Impex Ltd.</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>SRIVASAVI</t>
+          <t>STRIDERS</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -12983,17 +13016,17 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Striders Impex Ltd.</t>
+          <t>Studio LSD Ltd.</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>STRIDERS</t>
+          <t>STUDIOLSD</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -13003,17 +13036,17 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Studio LSD Ltd.</t>
+          <t>Suba Hotels Ltd.</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>STUDIOLSD</t>
+          <t>SUBAHOTELS</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -13023,17 +13056,17 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Suba Hotels Ltd.</t>
+          <t>Sundrex Oil Company Ltd.</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>SUBAHOTELS</t>
+          <t>SOCL</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -13043,17 +13076,17 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Sundrex Oil Company Ltd.</t>
+          <t>Sungarner Energies Ltd.</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>SOCL</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13063,12 +13096,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Sungarner Energies Ltd.</t>
+          <t>Sunlite Recycling Industries Ltd.</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>SUNLITE</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -13083,17 +13116,17 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Sunlite Recycling Industries Ltd.</t>
+          <t>Sunrest Lifescience Ltd.</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>SUNLITE</t>
+          <t>SUNREST</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -13103,17 +13136,17 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Sunrest Lifescience Ltd.</t>
+          <t>Suntech Infra Solutions Ltd.</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>SUNREST</t>
+          <t>SUNTECH</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -13123,17 +13156,17 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Suntech Infra Solutions Ltd.</t>
+          <t>Supreme Facility Management Ltd.</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>SUNTECH</t>
+          <t>SFML</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -13143,17 +13176,17 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Supreme Facility Management Ltd.</t>
+          <t>Supreme Power Equipment Ltd.</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>SFML</t>
+          <t>SUPREMEPWR</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13163,12 +13196,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Supreme Power Equipment Ltd.</t>
+          <t>Surani Steel Tubes Ltd.</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>SUPREMEPWR</t>
+          <t>SURANI</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -13183,12 +13216,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Surani Steel Tubes Ltd.</t>
+          <t>Swastik Pipe Ltd.</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>SURANI</t>
+          <t>SWASTIK</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -13203,17 +13236,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Swastik Pipe Ltd.</t>
+          <t>Sylvan Plyboard (India) Ltd.</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>SWASTIK</t>
+          <t>SYLVANPLY</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -13223,17 +13256,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Sylvan Plyboard (India) Ltd.</t>
+          <t>Synoptics Technologies Ltd.</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>SYLVANPLY</t>
+          <t>SYNOPTICS</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13243,12 +13276,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Synoptics Technologies Ltd.</t>
+          <t>Systango Technologies Ltd.</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>SYNOPTICS</t>
+          <t>SYSTANGO</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -13263,12 +13296,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Systango Technologies Ltd.</t>
+          <t>TAC INFOSEC Ltd.</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>SYSTANGO</t>
+          <t>TAC</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -13283,17 +13316,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>TAC INFOSEC Ltd.</t>
+          <t>Tankup Engineers Ltd.</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>TAC</t>
+          <t>TANKUP</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13303,17 +13336,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Tankup Engineers Ltd.</t>
+          <t>Tapi Fruit Processing Ltd.</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>TANKUP</t>
+          <t>TAPIFRUIT</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -13323,17 +13356,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Tapi Fruit Processing Ltd.</t>
+          <t>Taurian MPS Ltd.</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>TAPIFRUIT</t>
+          <t>TAURIAN</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13343,17 +13376,17 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Taurian MPS Ltd.</t>
+          <t>TBI Corn Ltd.</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>TAURIAN</t>
+          <t>TBI</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -13363,17 +13396,17 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>TBI Corn Ltd.</t>
+          <t>TechD Cybersecurity Ltd.</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>TBI</t>
+          <t>TECHD</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13383,17 +13416,17 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>TechD Cybersecurity Ltd.</t>
+          <t>TechEra Engineering (India) Ltd.</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>TECHD</t>
+          <t>TECHERA</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13403,17 +13436,17 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>TechEra Engineering (India) Ltd.</t>
+          <t>TEERTH GOPICON Ltd.</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>TECHERA</t>
+          <t>TGL</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -13423,17 +13456,17 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>TEERTH GOPICON Ltd.</t>
+          <t>Tejas Cargo India Ltd.</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>TGL</t>
+          <t>TEJASCARGO</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -13443,17 +13476,17 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Tejas Cargo India Ltd.</t>
+          <t>Thaai Casting Ltd.</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>TEJASCARGO</t>
+          <t>TCL</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -13463,17 +13496,17 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Thaai Casting Ltd.</t>
+          <t>Thinking Hats Entertainment Solutions Ltd.</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>TCL</t>
+          <t>THESL</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -13483,17 +13516,17 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Thinking Hats Entertainment Solutions Ltd.</t>
+          <t>Timescan Logistics (India) Ltd.</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>THESL</t>
+          <t>TIMESCAN</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13536,17 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Timescan Logistics (India) Ltd.</t>
+          <t>Transteel Seating Technologies Ltd.</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>TIMESCAN</t>
+          <t>TRANSTEEL</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -13523,17 +13556,17 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Transteel Seating Technologies Ltd.</t>
+          <t>Transwind Infra Ltd.</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>TRANSTEEL</t>
+          <t>TRANSWIND</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -13543,17 +13576,17 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Transwind Infra Ltd.</t>
+          <t>Trident Techlabs Ltd.</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>TRANSWIND</t>
+          <t>TECHLABS</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13563,12 +13596,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Trident Techlabs Ltd.</t>
+          <t>Tridhya Tech Ltd.</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>TECHLABS</t>
+          <t>TRIDHYA</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -13583,17 +13616,17 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Tridhya Tech Ltd.</t>
+          <t>Trom Industries Ltd.</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>TRIDHYA</t>
+          <t>TROM</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13603,17 +13636,17 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Trom Industries Ltd.</t>
+          <t>Trust Fintech Ltd.</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>TROM</t>
+          <t>TRUST</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13623,17 +13656,17 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Trust Fintech Ltd.</t>
+          <t>TSC India Ltd.</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>TSC</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -13643,17 +13676,17 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>TSC India Ltd.</t>
+          <t>Tunwal E-Motors Ltd.</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>TSC</t>
+          <t>TUNWAL</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -13663,12 +13696,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Tunwal E-Motors Ltd.</t>
+          <t>Ultra Wiring Connectivity System Ltd.</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>TUNWAL</t>
+          <t>UWCSL</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -13683,17 +13716,17 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Ultra Wiring Connectivity System Ltd.</t>
+          <t>Uma Converter Ltd.</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>UWCSL</t>
+          <t>UMA</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13703,17 +13736,17 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Uma Converter Ltd.</t>
+          <t>Unihealth Hospitals Ltd.</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>UMA</t>
+          <t>UNIHEALTH</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -13723,17 +13756,17 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Unihealth Hospitals Ltd.</t>
+          <t>Unilex Colours and Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>UNIHEALTH</t>
+          <t>UNILEX</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -13743,17 +13776,17 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Unilex Colours and Chemicals Ltd.</t>
+          <t>United Heat Transfer Ltd.</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>UNILEX</t>
+          <t>UHTL</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13763,17 +13796,17 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>United Heat Transfer Ltd.</t>
+          <t>Upsurge Seeds of Agriculture Ltd.</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>UHTL</t>
+          <t>USASEEDS</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -13783,17 +13816,17 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Upsurge Seeds of Agriculture Ltd.</t>
+          <t>Urban Enviro Waste Management Ltd.</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>USASEEDS</t>
+          <t>URBAN</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -13803,17 +13836,17 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Urban Enviro Waste Management Ltd.</t>
+          <t>Usha Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>URBAN</t>
+          <t>USHAFIN</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13856,17 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Usha Financial Services Ltd.</t>
+          <t>Ushanti Colour Chem Ltd.</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>USHAFIN</t>
+          <t>UCL</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -13843,17 +13876,17 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Ushanti Colour Chem Ltd.</t>
+          <t>Utssav CZ Gold Jewels Ltd.</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>UCL</t>
+          <t>UTSSAV</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -13863,17 +13896,17 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Utssav CZ Gold Jewels Ltd.</t>
+          <t>V Marc India Ltd.</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>UTSSAV</t>
+          <t>VMARCIND</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13883,17 +13916,17 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>V Marc India Ltd.</t>
+          <t>V R Infraspace Ltd.</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>VMARCIND</t>
+          <t>VR</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -13903,17 +13936,17 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>V R Infraspace Ltd.</t>
+          <t>V.L.Infraprojects Ltd.</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>VR</t>
+          <t>VLINFRA</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -13923,17 +13956,17 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>V.L.Infraprojects Ltd.</t>
+          <t>VADIVARHE SPECIALITY CHEMICALS Ltd.</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>VLINFRA</t>
+          <t>VSCL</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -13943,17 +13976,17 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>VADIVARHE SPECIALITY CHEMICALS Ltd.</t>
+          <t>Vaidya Sane Ayurved Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>VSCL</t>
+          <t>MADHAVBAUG</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -13963,17 +13996,17 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Vaidya Sane Ayurved Laboratories Ltd.</t>
+          <t>Value 360 Communications Ltd.</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>MADHAVBAUG</t>
+          <t>VALUE360</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -13983,17 +14016,17 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Value 360 Communications Ltd.</t>
+          <t>Vasa Denticity Ltd.</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>VALUE360</t>
+          <t>DENTALKART</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -14003,17 +14036,17 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Vasa Denticity Ltd.</t>
+          <t>Vdeal System Ltd.</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>DENTALKART</t>
+          <t>VDEAL</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14023,17 +14056,17 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Vdeal System Ltd.</t>
+          <t>Veekayem Fashion and Apparels Ltd.</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>VDEAL</t>
+          <t>VEEKAYEM</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -14043,17 +14076,17 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Veekayem Fashion and Apparels Ltd.</t>
+          <t>Vels Film International Ltd.</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>VEEKAYEM</t>
+          <t>VELS</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -14063,12 +14096,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Vels Film International Ltd.</t>
+          <t>Veritaas Advertising Ltd.</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>VELS</t>
+          <t>VERITAAS</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -14083,17 +14116,17 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Veritaas Advertising Ltd.</t>
+          <t>Vertexplus Technologies Ltd.</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>VERITAAS</t>
+          <t>VERTEXPLUS</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -14103,17 +14136,17 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Vertexplus Technologies Ltd.</t>
+          <t>Viaz Tyres Ltd.</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>VERTEXPLUS</t>
+          <t>VIAZ</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -14123,12 +14156,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Viaz Tyres Ltd.</t>
+          <t>Victory Electric Vehicles International Ltd.</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>VIAZ</t>
+          <t>VICTORYEV</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -14143,17 +14176,17 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Victory Electric Vehicles International Ltd.</t>
+          <t>Vigor Plast India Ltd.</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>VICTORYEV</t>
+          <t>VIGOR</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14163,17 +14196,17 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Vigor Plast India Ltd.</t>
+          <t>Vijaypd Ceutical Ltd.</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>VIGOR</t>
+          <t>VIJAYPD</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -14183,17 +14216,17 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Vijaypd Ceutical Ltd.</t>
+          <t>Vilas Transcore Ltd.</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>VIJAYPD</t>
+          <t>VILAS</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14203,17 +14236,17 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Vilas Transcore Ltd.</t>
+          <t>VILIN BIO MED Ltd.</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>VILAS</t>
+          <t>VILINBIO</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -14223,17 +14256,17 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>VILIN BIO MED Ltd.</t>
+          <t>Vinsys IT Services India Ltd.</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>VILINBIO</t>
+          <t>VINSYS</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -14243,17 +14276,17 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Vinsys IT Services India Ltd.</t>
+          <t>Vinyas Innovative Technologies Ltd.</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>VINSYS</t>
+          <t>VINYAS</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14263,17 +14296,17 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Vinyas Innovative Technologies Ltd.</t>
+          <t>Virtual Galaxy Infotech Ltd.</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>VINYAS</t>
+          <t>VGINFOTECH</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -14283,17 +14316,17 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Virtual Galaxy Infotech Ltd.</t>
+          <t>Visaman Global Sales Ltd.</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>VGINFOTECH</t>
+          <t>VISAMAN</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14303,17 +14336,17 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Visaman Global Sales Ltd.</t>
+          <t>Visdem Technosys Ltd.</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>VISAMAN</t>
+          <t>VISDEM</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -14323,17 +14356,17 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Visdem Technosys Ltd.</t>
+          <t>Vishnusurya Projects and Infra Ltd.</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>VISDEM</t>
+          <t>VISHNUINFR</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -14343,17 +14376,17 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Vishnusurya Projects and Infra Ltd.</t>
+          <t>Vishwas Agri Seeds Ltd.</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>VISHNUINFR</t>
+          <t>VISHWAS</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -14363,17 +14396,17 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Vishwas Agri Seeds Ltd.</t>
+          <t>Vision Infra Equipment Solutions Ltd.</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>VISHWAS</t>
+          <t>VIESL</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -14383,17 +14416,17 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Vision Infra Equipment Solutions Ltd.</t>
+          <t>Vivid Electromech Ltd.</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>VIESL</t>
+          <t>VIVIDEL</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14403,17 +14436,17 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Vivid Electromech Ltd.</t>
+          <t>Vivo Collaboration Solutions Ltd.</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>VIVIDEL</t>
+          <t>VIVO</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -14423,17 +14456,17 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Vivo Collaboration Solutions Ltd.</t>
+          <t>Voler Car Ltd.</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>VIVO</t>
+          <t>VOLERCAR</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -14443,17 +14476,17 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Voler Car Ltd.</t>
+          <t>Walpar Nutritions Ltd.</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>VOLERCAR</t>
+          <t>WALPAR</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -14463,17 +14496,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Walpar Nutritions Ltd.</t>
+          <t>Winny Immigration &amp; Education Services Ltd.</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>WALPAR</t>
+          <t>WINNY</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -14483,17 +14516,17 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Winny Immigration &amp; Education Services Ltd.</t>
+          <t>Winsol Engineers Ltd.</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>WINNY</t>
+          <t>WINSOL</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -14503,17 +14536,17 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Winsol Engineers Ltd.</t>
+          <t>Wise Travel India Ltd.</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>WINSOL</t>
+          <t>WTICAB</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -14523,17 +14556,17 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Wise Travel India Ltd.</t>
+          <t>Wol 3D India Ltd.</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>WTICAB</t>
+          <t>WOL3D</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14576,17 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Wol 3D India Ltd.</t>
+          <t>Womancart Ltd.</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>WOL3D</t>
+          <t>WOMANCART</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -14563,17 +14596,17 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Womancart Ltd.</t>
+          <t>Yaap Digital Ltd.</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>WOMANCART</t>
+          <t>YAAP</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -14583,17 +14616,17 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Yaap Digital Ltd.</t>
+          <t>Yash Optics &amp; Lens Ltd.</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>YAAP</t>
+          <t>YASHOPTICS</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -14603,17 +14636,17 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Yash Optics &amp; Lens Ltd.</t>
+          <t>Yasons Chemex Care Ltd.</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>YASHOPTICS</t>
+          <t>YCCL</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -14623,17 +14656,17 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Yasons Chemex Care Ltd.</t>
+          <t>Yudiz Solutions Ltd.</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>YCCL</t>
+          <t>YUDIZ</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -14643,17 +14676,17 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Yudiz Solutions Ltd.</t>
+          <t>Z-Tech (India) Ltd.</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>YUDIZ</t>
+          <t>ZTECH</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -14663,17 +14696,17 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Z-Tech (India) Ltd.</t>
+          <t>Zeal Global Services Ltd.</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>ZTECH</t>
+          <t>ZEAL</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -14683,35 +14716,15 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Zeal Global Services Ltd.</t>
+          <t>Zenith Drugs Ltd.</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>ZEAL</t>
+          <t>ZENITHDRUG</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="n">
-        <v>529</v>
-      </c>
-      <c r="B534" t="inlineStr">
-        <is>
-          <t>Zenith Drugs Ltd.</t>
-        </is>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>ZENITHDRUG</t>
-        </is>
-      </c>
-      <c r="D534" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15088.5</v>
+        <v>15203.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>656.0217391304348</v>
+        <v>658.1623376623376</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1330786621173423</v>
+        <v>0.1367151563268911</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.04329004329004329</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>73.23146484693693</v>
+        <v>74.68606253075644</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>82.67256445408107</v>
+        <v>83.10894375922692</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>42.93847181115781</v>
+        <v>43.43212613544151</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28168.57095315889</v>
+        <v>28585.38966694769</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.8668900787459917</v>
+        <v>0.8801786205818831</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>82.99799640693837</v>
+        <v>84.2870871181384</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>54448.48994722129</v>
+        <v>55474.58629242307</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.608608539432103</v>
+        <v>2.648791650135861</v>
       </c>
     </row>
     <row r="16">
@@ -3843,7 +3843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4066,6 +4066,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>15203.55</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.136715156327</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4106,7 +4139,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15203.55</v>
+        <v>15024.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.1</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1328125</v>
+        <v>0.0859375</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>658.1623376623376</v>
+        <v>658.1230836618486</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1367151563268911</v>
+        <v>0.1368636037969304</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04329004329004329</v>
+        <v>0.04380201489268506</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>86.71875</v>
+        <v>91.40625</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>74.68606253075644</v>
+        <v>74.74544151877217</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>83.10894375922692</v>
+        <v>86.40800745563165</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>43.43212613544151</v>
+        <v>43.46435111223765</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28585.38966694769</v>
+        <v>28604.89278334714</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.8801786205818831</v>
+        <v>0.9038261547191264</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>84.2870871181384</v>
+        <v>84.39450370745885</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>55474.58629242307</v>
+        <v>55541.97102406413</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.648791650135861</v>
+        <v>2.696649308254878</v>
       </c>
     </row>
     <row r="16">
@@ -3843,7 +3843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4099,6 +4099,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>15024.95</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.0859375</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.136863603797</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4139,7 +4172,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15024.95</v>
+        <v>15119.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.83</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.0859375</v>
+        <v>0.1328125</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>658.1230836618486</v>
+        <v>658.2085328689595</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1368636037969304</v>
+        <v>0.1368930072765195</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04380201489268506</v>
+        <v>0.043535045711798</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.40625</v>
+        <v>86.71875</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>74.74544151877217</v>
+        <v>74.75720291060782</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>86.40800745563165</v>
+        <v>83.13028587318234</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>43.46435111223765</v>
+        <v>43.47073401958684</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28604.89278334714</v>
+        <v>28612.80806176902</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.9038261547191264</v>
+        <v>0.8925003926681256</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>84.39450370745885</v>
+        <v>84.41578006528954</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>55541.97102406413</v>
+        <v>55563.18674776299</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.696649308254878</v>
+        <v>2.675044843939467</v>
       </c>
     </row>
     <row r="16">
@@ -3843,7 +3843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4135,6 +4135,39 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>15119.05</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.136893007277</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -4147,7 +4180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E533"/>
+  <dimension ref="A1:E544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4172,7 +4205,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -5402,17 +5435,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AVP Infracon Ltd.</t>
+          <t>Avience Biomedicals Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AVPINFRA</t>
+          <t>AVIENCE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5422,17 +5455,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B.A.G. Convergence Ltd.</t>
+          <t>AVP Infracon Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BAGDIGITAL</t>
+          <t>AVPINFRA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -5442,17 +5475,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Baba Food Processing (India) Ltd.</t>
+          <t>B.A.G. Convergence Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BABAFP</t>
+          <t>BAGDIGITAL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -5462,17 +5495,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Baheti Recycling Industries Ltd.</t>
+          <t>Baba Food Processing (India) Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BAHETI</t>
+          <t>BABAFP</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5482,17 +5515,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Balaji Phosphates Ltd.</t>
+          <t>Baheti Recycling Industries Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BALAJIPHOS</t>
+          <t>BAHETI</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5502,17 +5535,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Barflex Polyfilms Ltd.</t>
+          <t>Balaji Phosphates Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BARFLEX</t>
+          <t>BALAJIPHOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5522,17 +5555,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Basilic Fly Studio Ltd.</t>
+          <t>Barflex Polyfilms Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BASILIC</t>
+          <t>BARFLEX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5575,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Baweja Studios Ltd.</t>
+          <t>Basilic Fly Studio Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BAWEJA</t>
+          <t>BASILIC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5562,17 +5595,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BEACON TRUSTEESHIP Ltd.</t>
+          <t>Baweja Studios Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BEACON</t>
+          <t>BAWEJA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -5582,17 +5615,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BEW Engineering Ltd.</t>
+          <t>BEACON TRUSTEESHIP Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BEWLTD</t>
+          <t>BEACON</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5602,12 +5635,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bhadora Industries Ltd.</t>
+          <t>BEW Engineering Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BHADORA</t>
+          <t>BEWLTD</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5622,17 +5655,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bikewo Green Tech Ltd.</t>
+          <t>Bhadora Industries Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BIKEWO</t>
+          <t>BHADORA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5642,17 +5675,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Biopol Chemicals Ltd.</t>
+          <t>Bikewo Green Tech Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BIOPOL</t>
+          <t>BIKEWO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5662,17 +5695,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BLUE PEBBLE Ltd.</t>
+          <t>Bio Medica Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BLUEPEBBLE</t>
+          <t>BMLL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5682,17 +5715,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blue Water Logistics Ltd.</t>
+          <t>Biopol Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BLUEWATER</t>
+          <t>BIOPOL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5702,12 +5735,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bombay Metrics Supply Chain Ltd.</t>
+          <t>BLUE PEBBLE Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BMETRICS</t>
+          <t>BLUEPEBBLE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5722,17 +5755,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Boss Packaging Solutions Ltd.</t>
+          <t>Blue Water Logistics Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BOSS</t>
+          <t>BLUEWATER</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5775,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Brace Port Logistics Ltd.</t>
+          <t>Bombay Metrics Supply Chain Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BRACEPORT</t>
+          <t>BMETRICS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5762,17 +5795,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Brandman Retail Ltd.</t>
+          <t>Boss Packaging Solutions Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BRANDMAN</t>
+          <t>BOSS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5782,17 +5815,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bulkcorp International Ltd.</t>
+          <t>Brace Port Logistics Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BULKCORP</t>
+          <t>BRACEPORT</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5802,17 +5835,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>C K K Retail Mart Ltd.</t>
+          <t>Brandman Retail Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CKKRETAIL</t>
+          <t>BRANDMAN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5822,17 +5855,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C P S Shapers Ltd.</t>
+          <t>Bulkcorp International Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CPS</t>
+          <t>BULKCORP</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5842,17 +5875,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C2C Advanced Systems Ltd.</t>
+          <t>C K K Retail Mart Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>C2C</t>
+          <t>CKKRETAIL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5862,17 +5895,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cadsys (India) Ltd.</t>
+          <t>C P S Shapers Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CADSYS</t>
+          <t>CPS</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -5882,17 +5915,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Canarys Automations Ltd.</t>
+          <t>C2C Advanced Systems Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CANARYS</t>
+          <t>C2C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5902,17 +5935,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cash Ur Drive Marketing Ltd.</t>
+          <t>Cadsys (India) Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CUDML</t>
+          <t>CADSYS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -5922,17 +5955,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cedaar Textile Ltd.</t>
+          <t>Canarys Automations Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CEDAAR</t>
+          <t>CANARYS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5942,17 +5975,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cell Point (India) Ltd.</t>
+          <t>Cash Ur Drive Marketing Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CELLPOINT</t>
+          <t>CUDML</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -5962,17 +5995,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cellecor Gadgets Ltd.</t>
+          <t>Cedaar Textile Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CELLECOR</t>
+          <t>CEDAAR</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -5982,17 +6015,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chaman Metallics Ltd.</t>
+          <t>Cell Point (India) Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CMNL</t>
+          <t>CELLPOINT</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6002,17 +6035,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chamunda Electrical Ltd.</t>
+          <t>Cellecor Gadgets Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CHAMUNDA</t>
+          <t>CELLECOR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -6022,17 +6055,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chandan Healthcare Ltd.</t>
+          <t>Chaman Metallics Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CHANDAN</t>
+          <t>CMNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -6042,17 +6075,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Chavda Infra Ltd.</t>
+          <t>Chamunda Electrical Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CHAVDA</t>
+          <t>CHAMUNDA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -6062,17 +6095,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Chetana Education Ltd.</t>
+          <t>Chandan Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CHETANA</t>
+          <t>CHANDAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -6082,17 +6115,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Classic Electrodes (India) Ltd.</t>
+          <t>Chavda Infra Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CLASSICEIL</t>
+          <t>CHAVDA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -6102,17 +6135,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Clear Secured Services Ltd.</t>
+          <t>Chetana Education Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CSSL</t>
+          <t>CHETANA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -6122,17 +6155,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Committed Cargo Care Ltd.</t>
+          <t>Classic Electrodes (India) Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>COMMITTED</t>
+          <t>CLASSICEIL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6142,17 +6175,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Connplex Cinemas Ltd.</t>
+          <t>Clay Craft India Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CONNPLEX</t>
+          <t>CLAYCRAFT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -6162,17 +6195,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Continental Seeds and Chemicals Ltd.</t>
+          <t>Clear Secured Services Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CONTI</t>
+          <t>CSSL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -6182,17 +6215,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cool Caps Industries Ltd.</t>
+          <t>Committed Cargo Care Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>COOLCAPS</t>
+          <t>COMMITTED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6235,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Crayons Advertising Ltd.</t>
+          <t>Connplex Cinemas Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CRAYONS</t>
+          <t>CONNPLEX</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6222,17 +6255,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Creative Graphics Solutions India Ltd.</t>
+          <t>Continental Seeds and Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CGRAPHICS</t>
+          <t>CONTI</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -6242,17 +6275,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Crop Life Science Ltd.</t>
+          <t>Cool Caps Industries Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CLSL</t>
+          <t>COOLCAPS</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6262,17 +6295,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Curis Lifesciences Ltd.</t>
+          <t>Crayons Advertising Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CURIS</t>
+          <t>CRAYONS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -6282,17 +6315,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Current Infraprojects Ltd.</t>
+          <t>Creative Graphics Solutions India Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>CGRAPHICS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6302,17 +6335,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cyber Media Research &amp; Services Ltd.</t>
+          <t>Crop Life Science Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CMRSL</t>
+          <t>CLSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6322,17 +6355,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>D.K. Enterprises Global Ltd.</t>
+          <t>Curis Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DKEGL</t>
+          <t>CURIS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -6342,17 +6375,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Danish Power Ltd.</t>
+          <t>Current Infraprojects Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DANISH</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -6362,17 +6395,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Dar Credit &amp; Capital Ltd.</t>
+          <t>Cyber Media Research &amp; Services Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DCCL</t>
+          <t>CMRSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -6382,12 +6415,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DCG Cables &amp; Wires Ltd.</t>
+          <t>D.K. Enterprises Global Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DCG</t>
+          <t>DKEGL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6402,12 +6435,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>De Neers Tools Ltd.</t>
+          <t>Danish Power Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DENEERS</t>
+          <t>DANISH</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6422,17 +6455,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deccan Transcon Leasing Ltd.</t>
+          <t>Dar Credit &amp; Capital Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DECCANTRAN</t>
+          <t>DCCL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6442,12 +6475,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deem Roll Tech Ltd.</t>
+          <t>DCG Cables &amp; Wires Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>DEEM</t>
+          <t>DCG</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6462,17 +6495,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Delaplex Ltd.</t>
+          <t>De Neers Tools Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DELAPLEX</t>
+          <t>DENEERS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6482,17 +6515,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Delta Autocorp Ltd.</t>
+          <t>Deccan Transcon Leasing Ltd.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DELTIC</t>
+          <t>DECCANTRAN</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -6502,17 +6535,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dhanlaxmi Crop Science Ltd.</t>
+          <t>Deem Roll Tech Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DHANLAXMI</t>
+          <t>DEEM</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6522,17 +6555,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Dhansa Labs Ltd.</t>
+          <t>Delaplex Ltd.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>DHANSA</t>
+          <t>DELAPLEX</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -6542,17 +6575,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Dhanuka Infra Realty Ltd.</t>
+          <t>Delta Autocorp Ltd.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DIRL</t>
+          <t>DELTIC</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -6562,17 +6595,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dhara Rail Projects Ltd.</t>
+          <t>Dhanlaxmi Crop Science Ltd.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DHARARAIL</t>
+          <t>DHANLAXMI</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -6582,12 +6615,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dhariwalcorp Ltd.</t>
+          <t>Dhansa Labs Ltd.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DHARIWAL</t>
+          <t>DHANSA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6602,17 +6635,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Diensten Tech Ltd.</t>
+          <t>Dhanuka Infra Realty Ltd.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>DTL</t>
+          <t>DIRL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -6622,17 +6655,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Digikore Studios Ltd.</t>
+          <t>Dhara Rail Projects Ltd.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>DIGIKORE</t>
+          <t>DHARARAIL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -6642,17 +6675,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Divine Hira Jewellers Ltd.</t>
+          <t>Dhariwalcorp Ltd.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>DIVINEHIRA</t>
+          <t>DHARIWAL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6662,17 +6695,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Divine Power Energy Ltd.</t>
+          <t>Diensten Tech Ltd.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>DPEL</t>
+          <t>DTL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -6682,17 +6715,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Divyadhan Recycling Industries Ltd.</t>
+          <t>Digikore Studios Ltd.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>DIVYADHAN</t>
+          <t>DIGIKORE</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -6702,17 +6735,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Docmode Health Technologies Ltd.</t>
+          <t>Divine Hira Jewellers Ltd.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>DHTL</t>
+          <t>DIVINEHIRA</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -6722,17 +6755,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Drone Destination Ltd.</t>
+          <t>Divine Power Energy Ltd.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DRONE</t>
+          <t>DPEL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6742,17 +6775,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ducol Organics And Colours Ltd.</t>
+          <t>Divyadhan Recycling Industries Ltd.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DUCOL</t>
+          <t>DIVYADHAN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6795,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DUDIGITAL GLOBAL LTD.</t>
+          <t>Docmode Health Technologies Ltd.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DUGLOBAL</t>
+          <t>DHTL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6782,17 +6815,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Durlax Top Surface Ltd.</t>
+          <t>Drone Destination Ltd.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DURLAX</t>
+          <t>DRONE</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6802,17 +6835,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Dynamic Services &amp; Security Ltd.</t>
+          <t>Ducol Organics And Colours Ltd.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DYNAMIC</t>
+          <t>DUCOL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6822,12 +6855,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>E Factor Experiences Ltd.</t>
+          <t>DUDIGITAL GLOBAL LTD.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>EFACTOR</t>
+          <t>DUGLOBAL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6842,17 +6875,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>E To E Transportation Infrastructure Ltd.</t>
+          <t>Durlax Top Surface Ltd.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>E2ERAIL</t>
+          <t>DURLAX</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -6862,17 +6895,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ecoline Exim Ltd.</t>
+          <t>Dynamic Services &amp; Security Ltd.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ECOLINE</t>
+          <t>DYNAMIC</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -6882,17 +6915,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Effwa Infra &amp; Research Ltd.</t>
+          <t>E Factor Experiences Ltd.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>EFFWA</t>
+          <t>EFACTOR</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6902,17 +6935,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Electro Force (India) Ltd.</t>
+          <t>E To E Transportation Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>EFORCE</t>
+          <t>E2ERAIL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -6922,17 +6955,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Eleganz Interiors Ltd.</t>
+          <t>Ecoline Exim Ltd.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ELGNZ</t>
+          <t>ECOLINE</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6942,17 +6975,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EMA Partners India Ltd.</t>
+          <t>Effwa Infra &amp; Research Ltd.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>EMAPARTNER</t>
+          <t>EFFWA</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -6962,17 +6995,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Emerald Tyre Manufacturers Ltd.</t>
+          <t>Electro Force (India) Ltd.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ETML</t>
+          <t>EFORCE</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6982,17 +7015,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Emkay Taps and Cutting Tools Ltd.</t>
+          <t>Eleganz Interiors Ltd.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>EMKAYTOOLS</t>
+          <t>ELGNZ</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -7002,17 +7035,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Emkay Tools Ltd.</t>
+          <t>EMA Partners India Ltd.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ETL</t>
+          <t>EMAPARTNER</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -7022,17 +7055,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Encompass Design India Ltd.</t>
+          <t>Emerald Tyre Manufacturers Ltd.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ENCOMPAS</t>
+          <t>ETML</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -7042,17 +7075,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Energy Mission Machineries (India) Ltd.</t>
+          <t>Emkay Taps and Cutting Tools Ltd.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>EMMIL</t>
+          <t>EMKAYTOOLS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -7062,17 +7095,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Enfuse Solutions Ltd.</t>
+          <t>Emkay Tools Ltd.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ENFUSE</t>
+          <t>ETL</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7082,17 +7115,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Enser Communications Ltd.</t>
+          <t>Encompass Design India Ltd.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ENSER</t>
+          <t>ENCOMPAS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7135,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Envirotech Systems Ltd.</t>
+          <t>Energy Mission Machineries (India) Ltd.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ENVIRO</t>
+          <t>EMMIL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7122,17 +7155,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Eppeltone Engineers Ltd.</t>
+          <t>Enfuse Solutions Ltd.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>EEPL</t>
+          <t>ENFUSE</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7142,12 +7175,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EPW India Ltd.</t>
+          <t>Enser Communications Ltd.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>EPWINDIA</t>
+          <t>ENSER</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7162,17 +7195,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Esconet Technologies Ltd.</t>
+          <t>Envirotech Systems Ltd.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ESCONET</t>
+          <t>ENVIRO</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7182,17 +7215,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Esprit Stones Ltd.</t>
+          <t>Eppeltone Engineers Ltd.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ESPRIT</t>
+          <t>EEPL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7202,17 +7235,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Essen Speciality Films Ltd.</t>
+          <t>EPW India Ltd.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ESFL</t>
+          <t>EPWINDIA</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7222,17 +7255,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Excellent Wires and Packaging Ltd.</t>
+          <t>Esconet Technologies Ltd.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>EXCELLENT</t>
+          <t>ESCONET</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7242,17 +7275,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Exim Routes Ltd.</t>
+          <t>Esprit Stones Ltd.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>EXIMROUTES</t>
+          <t>ESPRIT</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Forest Materials</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -7262,17 +7295,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Falcon Technoprojects India Ltd.</t>
+          <t>Essen Speciality Films Ltd.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FALCONTECH</t>
+          <t>ESFL</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -7282,17 +7315,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Felix Industries Ltd.</t>
+          <t>Excellent Wires and Packaging Ltd.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>EXCELLENT</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7302,17 +7335,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Fidel Softech Ltd.</t>
+          <t>Exim Routes Ltd.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FIDEL</t>
+          <t>EXIMROUTES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Forest Materials</t>
         </is>
       </c>
     </row>
@@ -7322,17 +7355,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Finbud Financial Services Ltd.</t>
+          <t>Falcon Technoprojects India Ltd.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FINBUD</t>
+          <t>FALCONTECH</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -7342,17 +7375,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FlySBS Aviation Ltd.</t>
+          <t>Felix Industries Ltd.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>FLYSBS</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -7362,17 +7395,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Flywings Simulator Training Centre Ltd.</t>
+          <t>Fidel Softech Ltd.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FWSTC</t>
+          <t>FIDEL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7382,17 +7415,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Foce India Ltd.</t>
+          <t>Finbud Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>FOCE</t>
+          <t>FINBUD</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7402,17 +7435,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Fonebox Retail Ltd.</t>
+          <t>FlySBS Aviation Ltd.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>FONEBOX</t>
+          <t>FLYSBS</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -7422,17 +7455,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Forcas Studio Ltd.</t>
+          <t>Flywings Simulator Training Centre Ltd.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FORCAS</t>
+          <t>FWSTC</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -7442,17 +7475,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Forge Auto International Ltd.</t>
+          <t>Foce India Ltd.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>FORGEAUTO</t>
+          <t>FOCE</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -7462,17 +7495,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Freshara Agro Exports Ltd.</t>
+          <t>Fonebox Retail Ltd.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FRESHARA</t>
+          <t>FONEBOX</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -7482,17 +7515,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Frog Innovations Ltd.</t>
+          <t>Forcas Studio Ltd.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>FORCAS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -7502,17 +7535,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Gajanand International Ltd.</t>
+          <t>Forge Auto International Ltd.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>GAJANAND</t>
+          <t>FORGEAUTO</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -7522,17 +7555,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Galaxy Medicare Ltd.</t>
+          <t>Freshara Agro Exports Ltd.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>GML</t>
+          <t>FRESHARA</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7542,17 +7575,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ganesh Green Bharat Ltd.</t>
+          <t>Frog Innovations Ltd.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>GGBL</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -7562,17 +7595,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ganesh Infraworld Ltd.</t>
+          <t>Gajanand International Ltd.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>GANESHIN</t>
+          <t>GAJANAND</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -7582,17 +7615,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ganga Bath Fittings Ltd.</t>
+          <t>Galaxy Medicare Ltd.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>GANGABATH</t>
+          <t>GML</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -7602,12 +7635,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Gayatri Rubbers And Chemicals Ltd.</t>
+          <t>Ganesh Green Bharat Ltd.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>GRCL</t>
+          <t>GGBL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7622,12 +7655,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Giriraj Civil Developers Ltd.</t>
+          <t>Ganesh Infraworld Ltd.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>GIRIRAJ</t>
+          <t>GANESHIN</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -7642,17 +7675,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Global Pet Industries Ltd.</t>
+          <t>Ganga Bath Fittings Ltd.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>GLOBALPET</t>
+          <t>GANGABATH</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -7662,17 +7695,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Globesecure Technologies Ltd.</t>
+          <t>Gayatri Rubbers And Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>GSTL</t>
+          <t>GRCL</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7682,17 +7715,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Goldkart Jewels Ltd.</t>
+          <t>GenXAI Analytics Ltd.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>GOLDKART</t>
+          <t>GENXAI</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7702,17 +7735,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Goldstar Power Ltd.</t>
+          <t>Giriraj Civil Developers Ltd.</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>GOLDSTAR</t>
+          <t>GIRIRAJ</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -7722,17 +7755,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Goyal Salt Ltd.</t>
+          <t>Global Pet Industries Ltd.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>GOYALSALT</t>
+          <t>GLOBALPET</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7742,17 +7775,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>GP Eco Solutions India Ltd.</t>
+          <t>Globesecure Technologies Ltd.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>GPECO</t>
+          <t>GSTL</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7762,17 +7795,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Grand Continent Hotels Ltd.</t>
+          <t>Goldkart Jewels Ltd.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>GCHOTELS</t>
+          <t>GOLDKART</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -7782,17 +7815,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Graphisads Ltd.</t>
+          <t>Goldstar Power Ltd.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>GRAPHISAD</t>
+          <t>GOLDSTAR</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -7802,17 +7835,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Greenchef Appliances Ltd.</t>
+          <t>Goyal Salt Ltd.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>GREENCHEF</t>
+          <t>GOYALSALT</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7822,17 +7855,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Greenleaf Envirotech Ltd.</t>
+          <t>GP Eco Solutions India Ltd.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>GREENLEAF</t>
+          <t>GPECO</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7842,17 +7875,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Gretex Industries Ltd.</t>
+          <t>Grand Continent Hotels Ltd.</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>GRETEX</t>
+          <t>GCHOTELS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -7862,17 +7895,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>GRILL SPLENDOUR SERVICES Ltd.</t>
+          <t>Graphisads Ltd.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BIRDYS</t>
+          <t>GRAPHISAD</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -7882,12 +7915,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Grover Jewells Ltd.</t>
+          <t>Greenchef Appliances Ltd.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>GJL</t>
+          <t>GREENCHEF</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -7902,17 +7935,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>GSM Foils Ltd.</t>
+          <t>Greenleaf Envirotech Ltd.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>GSMFOILS</t>
+          <t>GREENLEAF</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -7922,17 +7955,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Gurunanak Agriculture India Ltd.</t>
+          <t>Gretex Industries Ltd.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>GURUNANAK</t>
+          <t>GRETEX</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7975,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Happy Square Outsourcing Services Ltd.</t>
+          <t>GRILL SPLENDOUR SERVICES Ltd.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>WHITEFORCE</t>
+          <t>BIRDYS</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -7962,17 +7995,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Hi-Green Carbon Ltd.</t>
+          <t>Grover Jewells Ltd.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>HIGREEN</t>
+          <t>GJL</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -7982,17 +8015,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Hoac Foods India Ltd.</t>
+          <t>GSM Foils Ltd.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>HOACFOODS</t>
+          <t>GSMFOILS</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8002,12 +8035,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Holmarc Opto-Mechatronics Ltd.</t>
+          <t>Gurunanak Agriculture India Ltd.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>HOLMARC</t>
+          <t>GURUNANAK</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -8022,17 +8055,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Homesfy Realty Ltd.</t>
+          <t>Happy Square Outsourcing Services Ltd.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>HOMESFY</t>
+          <t>WHITEFORCE</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -8042,17 +8075,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>HP Telecom India Ltd.</t>
+          <t>Happy Steels Ltd.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>HPTL</t>
+          <t>HAPPY</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -8062,17 +8095,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HRH Next Services Ltd.</t>
+          <t>Hi-Green Carbon Ltd.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>HRHNEXT</t>
+          <t>HIGREEN</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -8082,17 +8115,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>HVAX Technologies Ltd.</t>
+          <t>Hoac Foods India Ltd.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>HVAX</t>
+          <t>HOACFOODS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -8102,17 +8135,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IBL Finance Ltd.</t>
+          <t>Holmarc Opto-Mechatronics Ltd.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>IBLFL</t>
+          <t>HOLMARC</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8122,17 +8155,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Ideal Technoplast Industries Ltd.</t>
+          <t>Homesfy Realty Ltd.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>IDEALTECHO</t>
+          <t>HOMESFY</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -8142,17 +8175,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Identical Brains Studios Ltd.</t>
+          <t>HP Telecom India Ltd.</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>IDENTICAL</t>
+          <t>HPTL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -8162,17 +8195,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Indian Emulsifiers Ltd.</t>
+          <t>HRH Next Services Ltd.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>IEML</t>
+          <t>HRHNEXT</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -8182,17 +8215,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Indian Phosphate Ltd.</t>
+          <t>HVAX Technologies Ltd.</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>IPHL</t>
+          <t>HVAX</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -8202,17 +8235,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Indifra Ltd.</t>
+          <t>IBL Finance Ltd.</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>INDIFRA</t>
+          <t>IBLFL</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8222,17 +8255,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Infinium Pharmachem Ltd.</t>
+          <t>IC Electricals Company Ltd.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>INFINIUM</t>
+          <t>ICELCO</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8242,17 +8275,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Influx Healthtech Ltd.</t>
+          <t>Ideal Technoplast Industries Ltd.</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>INFLUX</t>
+          <t>IDEALTECHO</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8262,17 +8295,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Infollion Research Services Ltd.</t>
+          <t>Identical Brains Studios Ltd.</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>INFOLLION</t>
+          <t>IDENTICAL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -8282,17 +8315,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Innomet Advanced Materials Ltd.</t>
+          <t>Indian Emulsifiers Ltd.</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>INNOMET</t>
+          <t>IEML</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -8302,17 +8335,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Innovative Tyres &amp; Tubes Ltd.</t>
+          <t>Indian Phosphate Ltd.</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ITTL</t>
+          <t>IPHL</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -8322,17 +8355,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>INSPIRE FILMS Ltd.</t>
+          <t>Indifra Ltd.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>INSPIRE</t>
+          <t>INDIFRA</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -8342,17 +8375,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Integrated Personnel Services Ltd.</t>
+          <t>Infinium Pharmachem Ltd.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>IPSL</t>
+          <t>INFINIUM</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -8362,17 +8395,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Integrity Infrabuild Developers Ltd.</t>
+          <t>Influx Healthtech Ltd.</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>INTEGRITY</t>
+          <t>INFLUX</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -8382,17 +8415,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Interiors &amp; More Ltd.</t>
+          <t>Infollion Research Services Ltd.</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>INM</t>
+          <t>INFOLLION</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -8402,17 +8435,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Invicta Diagnostic Ltd.</t>
+          <t>Innomet Advanced Materials Ltd.</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>INVICTA</t>
+          <t>INNOMET</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -8422,17 +8455,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Ishan International Ltd.</t>
+          <t>Innovative Tyres &amp; Tubes Ltd.</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>ISHAN</t>
+          <t>ITTL</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -8442,17 +8475,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Italian Edibles Ltd.</t>
+          <t>INSPIRE FILMS Ltd.</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>ITALIANE</t>
+          <t>INSPIRE</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8495,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Iware Supplychain Services Ltd.</t>
+          <t>Integrated Personnel Services Ltd.</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>IWARE</t>
+          <t>IPSL</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -8482,17 +8515,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Jainam Ferro Alloys (I) Ltd.</t>
+          <t>Integrity Infrabuild Developers Ltd.</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>JAINAM</t>
+          <t>INTEGRITY</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -8502,17 +8535,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Jainik Power Cables Ltd.</t>
+          <t>Interiors &amp; More Ltd.</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>JAINIK</t>
+          <t>INM</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -8522,17 +8555,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Jalan Transolutions (India) Ltd.</t>
+          <t>Invicta Diagnostic Ltd.</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>JALAN</t>
+          <t>INVICTA</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -8542,12 +8575,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Jay Bee Laminations Ltd.</t>
+          <t>Ishan International Ltd.</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>JAYBEE</t>
+          <t>ISHAN</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -8562,17 +8595,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Jay Jalaram Technologies Ltd.</t>
+          <t>Italian Edibles Ltd.</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>KORE</t>
+          <t>ITALIANE</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8615,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Jayesh Logistics Ltd.</t>
+          <t>Iware Supplychain Services Ltd.</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>JAYESH</t>
+          <t>IWARE</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -8602,17 +8635,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Jeyyam Global Foods Ltd.</t>
+          <t>Jainam Ferro Alloys (I) Ltd.</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>JEYYAM</t>
+          <t>JAINAM</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -8622,17 +8655,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JFL Life Sciences Ltd.</t>
+          <t>Jainik Power Cables Ltd.</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>JFLLIFE</t>
+          <t>JAINIK</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -8642,17 +8675,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jiwanram Sheoduttrai Industries Ltd.</t>
+          <t>Jalan Transolutions (India) Ltd.</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>JIWANRAM</t>
+          <t>JALAN</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -8662,12 +8695,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jyoti Global Plast Ltd.</t>
+          <t>Jay Bee Laminations Ltd.</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>JYOTIGLOBL</t>
+          <t>JAYBEE</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -8682,17 +8715,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>K2 Infragen Ltd.</t>
+          <t>Jay Jalaram Technologies Ltd.</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>K2INFRA</t>
+          <t>KORE</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -8702,17 +8735,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Kabra Jewels Ltd.</t>
+          <t>Jayesh Logistics Ltd.</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>KKJEWELS</t>
+          <t>JAYESH</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -8722,17 +8755,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Kalana Ispat Ltd.</t>
+          <t>Jeyyam Global Foods Ltd.</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>KALANA</t>
+          <t>JEYYAM</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -8742,17 +8775,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Kandarp Digi Smart BPO Ltd.</t>
+          <t>JFL Life Sciences Ltd.</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>KANDARP</t>
+          <t>JFLLIFE</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -8762,17 +8795,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Karnika Industries Ltd.</t>
+          <t>Jiwanram Sheoduttrai Industries Ltd.</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>KARNIKA</t>
+          <t>JIWANRAM</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8782,12 +8815,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Kataria Industries Ltd.</t>
+          <t>Jyoti Global Plast Ltd.</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>KATARIA</t>
+          <t>JYOTIGLOBL</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -8802,17 +8835,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Kaushalya Logistics Ltd.</t>
+          <t>K2 Infragen Ltd.</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>KLL</t>
+          <t>K2INFRA</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -8822,17 +8855,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Kay Cee Energy &amp; Infra Ltd.</t>
+          <t>Kabra Jewels Ltd.</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>KCEIL</t>
+          <t>KKJEWELS</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -8842,17 +8875,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Kaytex Fabrics Ltd.</t>
+          <t>Kalana Ispat Ltd.</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>KAYTEX</t>
+          <t>KALANA</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8862,17 +8895,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>KCK INDUSTRIES Ltd.</t>
+          <t>Kandarp Digi Smart BPO Ltd.</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>KCK</t>
+          <t>KANDARP</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -8882,12 +8915,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Ken Enterprises Ltd.</t>
+          <t>Karnika Industries Ltd.</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>KARNIKA</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -8902,17 +8935,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>KHFM Hospitality And Facility Management Services Ltd.</t>
+          <t>Kataria Industries Ltd.</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>KHFM</t>
+          <t>KATARIA</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8922,17 +8955,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>KKV Agro Powers Ltd.</t>
+          <t>Kaushalya Logistics Ltd.</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>KKVAPOW</t>
+          <t>KLL</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -8942,17 +8975,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>KODY TECHNOLAB Ltd.</t>
+          <t>Kay Cee Energy &amp; Infra Ltd.</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>KODYTECH</t>
+          <t>KCEIL</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8962,17 +8995,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Konstelec Engineers Ltd.</t>
+          <t>Kaytex Fabrics Ltd.</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>KONSTELEC</t>
+          <t>KAYTEX</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -8982,17 +9015,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Kontor Space Ltd.</t>
+          <t>KCK INDUSTRIES Ltd.</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>KONTOR</t>
+          <t>KCK</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -9002,17 +9035,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Kore Digital Ltd.</t>
+          <t>Ken Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>KDL</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -9022,17 +9055,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Krishca Strapping Solutions Ltd.</t>
+          <t>KHFM Hospitality And Facility Management Services Ltd.</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>KRISHCA</t>
+          <t>KHFM</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -9042,17 +9075,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>KRM Ayurveda Ltd.</t>
+          <t>KKV Agro Powers Ltd.</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>KRMAYURVED</t>
+          <t>KKVAPOW</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -9062,17 +9095,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Lakshya Powertech Ltd.</t>
+          <t>KODY TECHNOLAB Ltd.</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>LAKSHYA</t>
+          <t>KODYTECH</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -9082,17 +9115,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Lamosaic India Ltd.</t>
+          <t>Konstelec Engineers Ltd.</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>LAMOSAIC</t>
+          <t>KONSTELEC</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9102,17 +9135,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Lead Reclaim And Rubber Products Ltd.</t>
+          <t>Kontor Space Ltd.</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>LRRPL</t>
+          <t>KONTOR</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -9122,17 +9155,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>LLOYDS LUXURIES Ltd.</t>
+          <t>Kore Digital Ltd.</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>LLOYDS</t>
+          <t>KDL</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -9142,17 +9175,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>M.V.K. Agro Food Product Ltd.</t>
+          <t>Krishca Strapping Solutions Ltd.</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>MVKAGRO</t>
+          <t>KRISHCA</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9162,17 +9195,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Macobs Technologies Ltd.</t>
+          <t>KRM Ayurveda Ltd.</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>MACOBSTECH</t>
+          <t>KRMAYURVED</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -9182,17 +9215,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Madhusudan Masala Ltd.</t>
+          <t>Lakshya Powertech Ltd.</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>MADHUSUDAN</t>
+          <t>LAKSHYA</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9235,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Madhya Pradesh Today Media Ltd.</t>
+          <t>Lamosaic India Ltd.</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>MPTODAY</t>
+          <t>LAMOSAIC</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -9222,17 +9255,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Magson Retail And Distribution Ltd.</t>
+          <t>Lead Reclaim And Rubber Products Ltd.</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>MAGSON</t>
+          <t>LRRPL</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9242,17 +9275,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Mahendra Realtors &amp; Infrastructure Ltd.</t>
+          <t>LLOYDS LUXURIES Ltd.</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>MRIL</t>
+          <t>LLOYDS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -9262,17 +9295,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Mahickra Chemicals Ltd.</t>
+          <t>M.V.K. Agro Food Product Ltd.</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>MAHICKRA</t>
+          <t>MVKAGRO</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -9282,17 +9315,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Maitreya Medicare Ltd.</t>
+          <t>Macobs Technologies Ltd.</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>MAITREYA</t>
+          <t>MACOBSTECH</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -9302,17 +9335,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Maks Energy Solutions India Ltd.</t>
+          <t>Madhusudan Masala Ltd.</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>MAKS</t>
+          <t>MADHUSUDAN</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -9322,17 +9355,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Manas Polymers and Energies Ltd.</t>
+          <t>Madhya Pradesh Today Media Ltd.</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>MPEL</t>
+          <t>MPTODAY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -9342,17 +9375,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Manav Infra Projects Ltd.</t>
+          <t>Magson Retail And Distribution Ltd.</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>MANAV</t>
+          <t>MAGSON</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -9362,17 +9395,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Mandeep Auto Industries Ltd.</t>
+          <t>Mahendra Realtors &amp; Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>MANDEEP</t>
+          <t>MRIL</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9382,17 +9415,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Mangalam Alloys Ltd.</t>
+          <t>Mahickra Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>MAL</t>
+          <t>MAHICKRA</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -9402,17 +9435,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Manglam Infra &amp; Engineering Ltd.</t>
+          <t>Maitreya Medicare Ltd.</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>MIEL</t>
+          <t>MAITREYA</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -9422,17 +9455,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Manilam Industries India Ltd.</t>
+          <t>Maks Energy Solutions India Ltd.</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>MANILAM</t>
+          <t>MAKS</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9442,17 +9475,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Marc Technocrats Ltd.</t>
+          <t>Manas Polymers and Energies Ltd.</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>MARC</t>
+          <t>MPEL</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9462,17 +9495,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Marco Cables &amp; Conductors Ltd.</t>
+          <t>Manav Infra Projects Ltd.</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>MARCO</t>
+          <t>MANAV</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9482,17 +9515,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Marinetrans India Ltd.</t>
+          <t>Mandeep Auto Industries Ltd.</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>MARINETRAN</t>
+          <t>MANDEEP</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -9502,17 +9535,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Marushika Technology Ltd.</t>
+          <t>Mangalam Alloys Ltd.</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>MARUSHIKA</t>
+          <t>MAL</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9522,17 +9555,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Marvel Decor Ltd.</t>
+          <t>Manglam Infra &amp; Engineering Ltd.</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>MDL</t>
+          <t>MIEL</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -9542,17 +9575,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Mason Infratech Ltd.</t>
+          <t>Manilam Industries India Ltd.</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>MASON</t>
+          <t>MANILAM</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -9562,17 +9595,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Master Components Ltd.</t>
+          <t>Marc Technocrats Ltd.</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>MASTER</t>
+          <t>MARC</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -9582,17 +9615,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Matrix Geo Solutions Ltd.</t>
+          <t>Marco Cables &amp; Conductors Ltd.</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>MGSL</t>
+          <t>MARCO</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9602,17 +9635,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Maxposure Ltd.</t>
+          <t>Marinetrans India Ltd.</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>MAXPOSURE</t>
+          <t>MARINETRAN</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -9622,17 +9655,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Maxvolt Energy Industries Ltd.</t>
+          <t>Marushika Technology Ltd.</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>MAXVOLT</t>
+          <t>MARUSHIKA</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -9642,17 +9675,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Mayasheel Ventures Ltd.</t>
+          <t>Marvel Decor Ltd.</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>MAYASHEEL</t>
+          <t>MDL</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -9662,17 +9695,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Mcon Rasayan India Ltd.</t>
+          <t>Mason Infratech Ltd.</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>MCON</t>
+          <t>MASON</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -9682,17 +9715,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Medicamen Organics Ltd.</t>
+          <t>Master Components Ltd.</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>MEDIORG</t>
+          <t>MASTER</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9702,17 +9735,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Medistep Healthcare Ltd.</t>
+          <t>Matrix Geo Solutions Ltd.</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>MEDISTEP</t>
+          <t>MGSL</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -9722,17 +9755,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Mega Flex Plastics Ltd.</t>
+          <t>Maxposure Ltd.</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>MEGAFLEX</t>
+          <t>MAXPOSURE</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -9742,17 +9775,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Megatherm Induction Ltd.</t>
+          <t>Maxvolt Energy Industries Ltd.</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>MEGATHERM</t>
+          <t>MAXVOLT</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -9762,17 +9795,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Micropro Software Solutions Ltd.</t>
+          <t>Mayasheel Ventures Ltd.</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>MICROPRO</t>
+          <t>MAYASHEEL</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9782,17 +9815,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>MILTON INDUSTRIES LTD.</t>
+          <t>Mcon Rasayan India Ltd.</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>MILTON</t>
+          <t>MCON</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -9802,17 +9835,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Mobilise App Lab Ltd.</t>
+          <t>Medicamen Organics Ltd.</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>MOBILISE</t>
+          <t>MEDIORG</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -9822,17 +9855,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Mohini Health &amp; Hygiene Ltd.</t>
+          <t>Medistep Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>MHHL</t>
+          <t>MEDISTEP</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -9842,17 +9875,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Mono Pharmacare Ltd.</t>
+          <t>Mega Flex Plastics Ltd.</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>MONOPHARMA</t>
+          <t>MEGAFLEX</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9862,12 +9895,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Monolithisch India Ltd.</t>
+          <t>Megatherm Induction Ltd.</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>MONOLITH</t>
+          <t>MEGATHERM</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -9882,17 +9915,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Mos Utility Ltd.</t>
+          <t>Micropro Software Solutions Ltd.</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>MICROPRO</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -9902,17 +9935,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Moving Media Entertainment Ltd.</t>
+          <t>MILTON INDUSTRIES LTD.</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>MMEL</t>
+          <t>MILTON</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -9922,17 +9955,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Moxsh Overseas Educon Ltd.</t>
+          <t>Mobilise App Lab Ltd.</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>MOXSH</t>
+          <t>MOBILISE</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -9942,17 +9975,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Munish Forge Ltd.</t>
+          <t>Mohini Health &amp; Hygiene Ltd.</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>MUNISH</t>
+          <t>MHHL</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -9962,17 +9995,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>My Mudra Fincorp Ltd.</t>
+          <t>Mono Pharmacare Ltd.</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>MYMUDRA</t>
+          <t>MONOPHARMA</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -9982,17 +10015,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>N R Vandana Tex Industries Ltd.</t>
+          <t>Monolithisch India Ltd.</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>NRVANDANA</t>
+          <t>MONOLITH</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10002,17 +10035,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Naman Industries Proxima Ltd.</t>
+          <t>Mos Utility Ltd.</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>NAMAN</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -10022,17 +10055,17 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Namo eWaste Management Ltd.</t>
+          <t>Moving Media Entertainment Ltd.</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>NAMOEWASTE</t>
+          <t>MMEL</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10042,17 +10075,17 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Neelam Linens and Garments (India) Ltd.</t>
+          <t>Moxsh Overseas Educon Ltd.</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>NEELAM</t>
+          <t>MOXSH</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -10062,17 +10095,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Neochem Bio Solutions Ltd.</t>
+          <t>Munish Forge Ltd.</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>NEOCHEM</t>
+          <t>MUNISH</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10082,17 +10115,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Nephro Care India Ltd.</t>
+          <t>My Mudra Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>NEPHROCARE</t>
+          <t>MYMUDRA</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -10102,17 +10135,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Neptune Petrochemicals Ltd.</t>
+          <t>N R Vandana Tex Industries Ltd.</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>NEPTUNE</t>
+          <t>NRVANDANA</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -10122,17 +10155,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>NET AVENUE TECHNOLOGIES Ltd.</t>
+          <t>Naman Industries Proxima Ltd.</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>CBAZAAR</t>
+          <t>NAMAN</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -10142,17 +10175,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Newjaisa Technologies Ltd.</t>
+          <t>Namo eWaste Management Ltd.</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>NEWJAISA</t>
+          <t>NAMOEWASTE</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -10162,17 +10195,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Newmalayalam Steel Ltd.</t>
+          <t>Neelam Linens and Garments (India) Ltd.</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>NMSTEEL</t>
+          <t>NEELAM</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -10182,17 +10215,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Nidan Laboratories And Healthcare Ltd.</t>
+          <t>Neochem Bio Solutions Ltd.</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>NIDAN</t>
+          <t>NEOCHEM</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -10202,17 +10235,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>NIKITA GREENTECH RECYCLING Ltd.</t>
+          <t>Nephro Care India Ltd.</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>NIKITA</t>
+          <t>NEPHROCARE</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Forest Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -10222,17 +10255,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Nirman Agri Genetics Ltd.</t>
+          <t>Neptune Petrochemicals Ltd.</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>NIRMAN</t>
+          <t>NEPTUNE</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -10242,17 +10275,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>OBSC Perfection Ltd.</t>
+          <t>NET AVENUE TECHNOLOGIES Ltd.</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>CBAZAAR</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -10262,17 +10295,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Omfurn India Ltd.</t>
+          <t>Newjaisa Technologies Ltd.</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>OMFURN</t>
+          <t>NEWJAISA</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -10282,17 +10315,17 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>On Door Concepts Ltd.</t>
+          <t>Newmalayalam Steel Ltd.</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>ONDOOR</t>
+          <t>NMSTEEL</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10302,17 +10335,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Oneclick Logistics India Ltd.</t>
+          <t>NFP Sampoorna Foods Ltd.</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>OLIL</t>
+          <t>NFPSAMPOOR</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -10322,12 +10355,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Onyx Biotec Ltd.</t>
+          <t>Nidan Laboratories And Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>ONYX</t>
+          <t>NIDAN</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -10342,17 +10375,17 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Optivalue Tek Consulting Ltd.</t>
+          <t>NIKITA GREENTECH RECYCLING Ltd.</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>OPTIVALUE</t>
+          <t>NIKITA</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Forest Materials</t>
         </is>
       </c>
     </row>
@@ -10362,17 +10395,17 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Oriana Power Ltd.</t>
+          <t>Nirman Agri Genetics Ltd.</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>ORIANA</t>
+          <t>NIRMAN</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -10382,17 +10415,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Osel Devices Ltd.</t>
+          <t>OBSC Perfection Ltd.</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>OSELDEVICE</t>
+          <t>OBSCP</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -10402,17 +10435,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Owais Metal and Mineral Processing Ltd.</t>
+          <t>Omfurn India Ltd.</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>OWAIS</t>
+          <t>OMFURN</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -10422,17 +10455,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>P S Raj Steels Ltd.</t>
+          <t>On Door Concepts Ltd.</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>PSRAJ</t>
+          <t>ONDOOR</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -10442,17 +10475,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>P. E. Analytics Ltd.</t>
+          <t>Oneclick Logistics India Ltd.</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>PROPEQUITY</t>
+          <t>OLIL</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10462,17 +10495,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Paragon Fine and Speciality Chemical Ltd.</t>
+          <t>Onyx Biotec Ltd.</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>PARAGON</t>
+          <t>ONYX</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -10482,12 +10515,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Paramatrix Technologies Ltd.</t>
+          <t>Optivalue Tek Consulting Ltd.</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>PARAMATRIX</t>
+          <t>OPTIVALUE</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -10502,17 +10535,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PARAMOUNT DYE TEC Ltd.</t>
+          <t>Oriana Power Ltd.</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>PARAMOUNT</t>
+          <t>ORIANA</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10522,17 +10555,17 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Paramount Speciality Forgings Ltd.</t>
+          <t>Osel Devices Ltd.</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>PSFL</t>
+          <t>OSELDEVICE</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -10542,17 +10575,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PARAMPARA DAIRY DELIGHTS LTD.</t>
+          <t>Owais Metal and Mineral Processing Ltd.</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>PARAMPARA</t>
+          <t>OWAIS</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -10562,12 +10595,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Parth Electricals &amp; Engineering Ltd.</t>
+          <t>P S Raj Steels Ltd.</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>PARTH</t>
+          <t>PSRAJ</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -10582,17 +10615,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Party Cruisers Ltd.</t>
+          <t>P. E. Analytics Ltd.</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>PARTYCRUS</t>
+          <t>PROPEQUITY</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -10602,17 +10635,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Patil Automation Ltd.</t>
+          <t>Paragon Fine and Speciality Chemical Ltd.</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>PATILAUTOM</t>
+          <t>PARAGON</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10655,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PATTECH FITWELL TUBE COMPONENTS Ltd.</t>
+          <t>Paramatrix Technologies Ltd.</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>PATTECH</t>
+          <t>PARAMATRIX</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -10642,17 +10675,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Pelatro Ltd.</t>
+          <t>PARAMOUNT DYE TEC Ltd.</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>PELATRO</t>
+          <t>PARAMOUNT</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -10662,12 +10695,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Pentagon Rubber Ltd.</t>
+          <t>Paramount Speciality Forgings Ltd.</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>PENTAGON</t>
+          <t>PSFL</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -10682,17 +10715,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Petro Carbon and Chemicals Ltd.</t>
+          <t>PARAMPARA DAIRY DELIGHTS LTD.</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>PCCL</t>
+          <t>PARAMPARA</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10702,17 +10735,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Phantom Digital Effects Ltd.</t>
+          <t>Parth Electricals &amp; Engineering Ltd.</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>PHANTOMFX</t>
+          <t>PARTH</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10722,17 +10755,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Phoenix Overseas Ltd.</t>
+          <t>Party Cruisers Ltd.</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>PHOGLOBAL</t>
+          <t>PARTYCRUS</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -10742,17 +10775,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Picturepost Studios Ltd.</t>
+          <t>Patil Automation Ltd.</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>PPSL</t>
+          <t>PATILAUTOM</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10762,17 +10795,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Plada Infotech Services Ltd.</t>
+          <t>Pelatro Ltd.</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>PLADAINFO</t>
+          <t>PELATRO</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -10782,12 +10815,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Polysil Irrigation Systems Ltd.</t>
+          <t>Pentagon Rubber Ltd.</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>POLYSIL</t>
+          <t>PENTAGON</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -10802,17 +10835,17 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Positron Energy Ltd.</t>
+          <t>Petro Carbon and Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>POSITRON</t>
+          <t>PCCL</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -10822,12 +10855,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Pramara Promotions Ltd.</t>
+          <t>Phantom Digital Effects Ltd.</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>PRAMARA</t>
+          <t>PHANTOMFX</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -10842,12 +10875,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Pranik Logistics Ltd.</t>
+          <t>Phoenix Overseas Ltd.</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>PRANIK</t>
+          <t>PHOGLOBAL</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -10862,17 +10895,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Pratham EPC Projects Ltd.</t>
+          <t>Picturepost Studios Ltd.</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>PRATHAM</t>
+          <t>PPSL</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -10882,17 +10915,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Precision Metaliks Ltd.</t>
+          <t>Plada Infotech Services Ltd.</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>PRECISION</t>
+          <t>PLADAINFO</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10902,17 +10935,17 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Premier Roadlines Ltd.</t>
+          <t>Polysil Irrigation Systems Ltd.</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>PRLIND</t>
+          <t>POLYSIL</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10922,17 +10955,17 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Premium Plast Ltd.</t>
+          <t>Positron Energy Ltd.</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>POSITRON</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10942,17 +10975,17 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Presstonic Engineering Ltd.</t>
+          <t>Pramara Promotions Ltd.</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>PRESSTONIC</t>
+          <t>PRAMARA</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -10962,17 +10995,17 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Prime Cable Industries Ltd.</t>
+          <t>Pranik Logistics Ltd.</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>PRIMECAB</t>
+          <t>PRANIK</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10982,17 +11015,17 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Pritika Engineering Components Ltd.</t>
+          <t>Pratham EPC Projects Ltd.</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>PRITIKA</t>
+          <t>PRATHAM</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -11002,17 +11035,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Prizor Viztech Ltd.</t>
+          <t>Precision Metaliks Ltd.</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>PRIZOR</t>
+          <t>PRECISION</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -11022,17 +11055,17 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Pro FX Tech Ltd.</t>
+          <t>Premier Roadlines Ltd.</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>PROFX</t>
+          <t>PRLIND</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11042,17 +11075,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Prolife Industries Ltd.</t>
+          <t>Premium Plast Ltd.</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>PROLIFE</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -11062,17 +11095,17 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Proventus Agrocom Ltd.</t>
+          <t>Presstonic Engineering Ltd.</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>PROV</t>
+          <t>PRESSTONIC</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11082,17 +11115,17 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Pulz Electronics Ltd.</t>
+          <t>Prime Cable Industries Ltd.</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>PULZ</t>
+          <t>PRIMECAB</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11102,17 +11135,17 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Purple United Sales Ltd.</t>
+          <t>Pritika Engineering Components Ltd.</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>PURPLEUTED</t>
+          <t>PRITIKA</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -11122,12 +11155,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Purv Flexipack Ltd.</t>
+          <t>Prizor Viztech Ltd.</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>PURVFLEXI</t>
+          <t>PRIZOR</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -11142,12 +11175,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Pushpa Jewellers Ltd.</t>
+          <t>Pro FX Tech Ltd.</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>PUSHPA</t>
+          <t>PROFX</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -11162,17 +11195,17 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>QUADPRO ITES Ltd.</t>
+          <t>Prolife Industries Ltd.</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>QUADPRO</t>
+          <t>PROLIFE</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11182,17 +11215,17 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Quality Foils (India) Ltd.</t>
+          <t>Proventus Agrocom Ltd.</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>QFIL</t>
+          <t>PROV</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -11202,17 +11235,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Quest Laboratories Ltd.</t>
+          <t>Pulz Electronics Ltd.</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>QUESTLAB</t>
+          <t>PULZ</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -11222,17 +11255,17 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Quicktouch Technologies Ltd.</t>
+          <t>Purple United Sales Ltd.</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>QUICKTOUCH</t>
+          <t>PURPLEUTED</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -11242,17 +11275,17 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>QVC Exports Ltd.</t>
+          <t>Purv Flexipack Ltd.</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>QVCEL</t>
+          <t>PURVFLEXI</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11262,17 +11295,17 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Rachana Infrastructure Ltd.</t>
+          <t>Pushpa Jewellers Ltd.</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>RILINFRA</t>
+          <t>PUSHPA</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -11282,17 +11315,17 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Radiowalla Network Ltd.</t>
+          <t>Q-Line Biotech Ltd.</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>RADIOWALLA</t>
+          <t>QLINE</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11302,17 +11335,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Rajgor Castor Derivatives Ltd.</t>
+          <t>QUADPRO ITES Ltd.</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>RCDL</t>
+          <t>QUADPRO</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11322,17 +11355,17 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Rajputana Biodiesel Ltd.</t>
+          <t>Quality Foils (India) Ltd.</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>RAJPUTANA</t>
+          <t>QFIL</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11342,17 +11375,17 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Rajputana Industries Ltd.</t>
+          <t>Quest Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>RAJINDLTD</t>
+          <t>QUESTLAB</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11362,17 +11395,17 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Rama Telecom Ltd.</t>
+          <t>Quicktouch Technologies Ltd.</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>RTL</t>
+          <t>QUICKTOUCH</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11382,17 +11415,17 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Ramdevbaba Solvent Ltd.</t>
+          <t>QVC Exports Ltd.</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>RBS</t>
+          <t>QVCEL</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -11402,17 +11435,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Rapid Fleet Management Services Ltd.</t>
+          <t>Rachana Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>RAPIDFLEET</t>
+          <t>RILINFRA</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -11422,17 +11455,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Rappid Valves (India) Ltd.</t>
+          <t>Radiowalla Network Ltd.</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>RAPPID</t>
+          <t>RADIOWALLA</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -11442,17 +11475,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>RBM Infracon Ltd.</t>
+          <t>Rajgor Castor Derivatives Ltd.</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>RBMINFRA</t>
+          <t>RCDL</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -11462,17 +11495,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Readymix Construction Machinery Ltd.</t>
+          <t>Rajputana Biodiesel Ltd.</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>READYMIX</t>
+          <t>RAJPUTANA</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -11482,12 +11515,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Refractory Shapes Ltd.</t>
+          <t>Rajputana Industries Ltd.</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>REFRACTORY</t>
+          <t>RAJINDLTD</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -11502,17 +11535,17 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Remus Pharmaceuticals Ltd.</t>
+          <t>Rama Telecom Ltd.</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>REMUS</t>
+          <t>RTL</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -11522,17 +11555,17 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Renol Polychem Ltd.</t>
+          <t>Ramdevbaba Solvent Ltd.</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>RNPL</t>
+          <t>RBS</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -11542,17 +11575,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Rex Pipes and Cables Industries Ltd.</t>
+          <t>Rapid Fleet Management Services Ltd.</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>REXPIPES</t>
+          <t>RAPIDFLEET</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11562,17 +11595,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Rexpro Enterprises Ltd.</t>
+          <t>Rappid Valves (India) Ltd.</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>REXPRO</t>
+          <t>RAPPID</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11582,17 +11615,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Richa Info Systems Ltd.</t>
+          <t>RBM Infracon Ltd.</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>RICHA</t>
+          <t>RBMINFRA</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -11602,17 +11635,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Rite Zone Chemcon India Ltd.</t>
+          <t>Readymix Construction Machinery Ltd.</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>RITEZONE</t>
+          <t>READYMIX</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11622,17 +11655,17 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>RNFI Services Ltd.</t>
+          <t>Refractory Shapes Ltd.</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>RNFI</t>
+          <t>REFRACTORY</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11642,17 +11675,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Rockingdeals Circular Economy Ltd.</t>
+          <t>Remus Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>ROCKINGDCE</t>
+          <t>REMUS</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11662,17 +11695,17 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Rox Hi-Tech Ltd.</t>
+          <t>Renol Polychem Ltd.</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>ROXHITECH</t>
+          <t>RNPL</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11682,12 +11715,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Royal Arc Electrodes Ltd.</t>
+          <t>Rex Pipes and Cables Industries Ltd.</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>ROYALARC</t>
+          <t>REXPIPES</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -11702,17 +11735,17 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Rulka Electricals Ltd.</t>
+          <t>Rexpro Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>RULKA</t>
+          <t>REXPRO</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -11722,17 +11755,17 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>S A Tech Software India Ltd.</t>
+          <t>RFBL Flexi Pack Ltd.</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>SATECH</t>
+          <t>RFBL</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11742,17 +11775,17 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>S D Retail Ltd.</t>
+          <t>Richa Info Systems Ltd.</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>SDREAMS</t>
+          <t>RICHA</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11762,17 +11795,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>S J Logistics (India) Ltd.</t>
+          <t>Rite Zone Chemcon India Ltd.</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>SJLOGISTIC</t>
+          <t>RITEZONE</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11782,17 +11815,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Saakshi Medtech and Panels Ltd.</t>
+          <t>RNFI Services Ltd.</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>SAAKSHI</t>
+          <t>RNFI</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11802,17 +11835,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Sabar Flex India Ltd.</t>
+          <t>Rockingdeals Circular Economy Ltd.</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>SABAR</t>
+          <t>ROCKINGDCE</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11822,17 +11855,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Sacheerome Ltd.</t>
+          <t>Rox Hi-Tech Ltd.</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>SACHEEROME</t>
+          <t>ROXHITECH</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11842,17 +11875,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Sadhav Shipping Ltd.</t>
+          <t>Royal Arc Electrodes Ltd.</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>SADHAV</t>
+          <t>ROYALARC</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11862,17 +11895,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Safe Enterprises Retail Fixtures Ltd.</t>
+          <t>Rulka Electricals Ltd.</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>SAFEENTP</t>
+          <t>RULKA</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11882,17 +11915,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Sahaj Solar Ltd.</t>
+          <t>S A Tech Software India Ltd.</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>SAHAJSOLAR</t>
+          <t>SATECH</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11902,17 +11935,17 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Sahana System Ltd.</t>
+          <t>S D Retail Ltd.</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>SAHANA</t>
+          <t>SDREAMS</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -11922,17 +11955,17 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Sahasra Electronic Solutions Ltd.</t>
+          <t>S J Logistics (India) Ltd.</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>SAHASRA</t>
+          <t>SJLOGISTIC</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -11942,17 +11975,17 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Saj Hotels Ltd.</t>
+          <t>Saakshi Medtech and Panels Ltd.</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>SAJHOTELS</t>
+          <t>SAAKSHI</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11962,17 +11995,17 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Samay Project Services Ltd.</t>
+          <t>Sabar Flex India Ltd.</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>SAMAY</t>
+          <t>SABAR</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11982,17 +12015,17 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Sameera Agro And Infra Ltd.</t>
+          <t>Sacheerome Ltd.</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>SAIFL</t>
+          <t>SACHEEROME</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -12002,17 +12035,17 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Sangani Hospitals Ltd.</t>
+          <t>Sadhav Shipping Ltd.</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>SANGANI</t>
+          <t>SADHAV</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12022,17 +12055,17 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Sar Televenture Ltd.</t>
+          <t>Safe Enterprises Retail Fixtures Ltd.</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>SARTELE</t>
+          <t>SAFEENTP</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -12042,17 +12075,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Saroja Pharma Industries India Ltd.</t>
+          <t>Sahaj Solar Ltd.</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>SAROJA</t>
+          <t>SAHAJSOLAR</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12062,17 +12095,17 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Sat Kartar Life Ltd.</t>
+          <t>Sahana System Ltd.</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>SATKARTAR</t>
+          <t>SAHANA</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -12082,17 +12115,17 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Sathlokhar Synergys E&amp;C Global Ltd.</t>
+          <t>Sahasra Electronic Solutions Ltd.</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>SSEGL</t>
+          <t>SAHASRA</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12102,17 +12135,17 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Sati Poly Plast Ltd.</t>
+          <t>Saj Hotels Ltd.</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>SATIPOLY</t>
+          <t>SAJHOTELS</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -12122,17 +12155,17 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Sattva Engineering Construction Ltd.</t>
+          <t>Samay Project Services Ltd.</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>SATTVAENGG</t>
+          <t>SAMAY</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -12142,17 +12175,17 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Savy Infra and Logistics Ltd.</t>
+          <t>Sameera Agro And Infra Ltd.</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>SAVY</t>
+          <t>SAIFL</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12162,17 +12195,17 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Sawaliya Food Products Ltd.</t>
+          <t>Sangani Hospitals Ltd.</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>SAWALIYA</t>
+          <t>SANGANI</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -12182,17 +12215,17 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Sellowrap Industries Ltd.</t>
+          <t>Sar Televenture Ltd.</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>SELLOWRAP</t>
+          <t>SARTELE</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -12202,17 +12235,17 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Service Care Ltd.</t>
+          <t>Saroja Pharma Industries India Ltd.</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>SERVICE</t>
+          <t>SAROJA</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -12222,17 +12255,17 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Shanthala FMCG Products Ltd.</t>
+          <t>Sat Kartar Life Ltd.</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>SHANTHALA</t>
+          <t>SATKARTAR</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -12242,17 +12275,17 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Sharp Chucks and Machines Ltd.</t>
+          <t>Sathlokhar Synergys E&amp;C Global Ltd.</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>SCML</t>
+          <t>SSEGL</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -12262,17 +12295,17 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Sheel Biotech Ltd.</t>
+          <t>Sati Poly Plast Ltd.</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>SHEEL</t>
+          <t>SATIPOLY</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12282,17 +12315,17 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Sheetal Universal Ltd.</t>
+          <t>Sattva Engineering Construction Ltd.</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SHEETAL</t>
+          <t>SATTVAENGG</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -12302,17 +12335,17 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Shera Energy Ltd.</t>
+          <t>Savy Infra and Logistics Ltd.</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>SHERA</t>
+          <t>SAVY</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -12322,17 +12355,17 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Shigan Quantum Technologies Ltd.</t>
+          <t>Sawaliya Food Products Ltd.</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>SHIGAN</t>
+          <t>SAWALIYA</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12342,17 +12375,17 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Shivalic Power Control Ltd.</t>
+          <t>Sellowrap Industries Ltd.</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>SPCL</t>
+          <t>SELLOWRAP</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -12362,17 +12395,17 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Shivashrit Foods Ltd.</t>
+          <t>Service Care Ltd.</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>SHIVASHRIT</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12382,17 +12415,17 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Shree Karni Fabcom Ltd.</t>
+          <t>Shanthala FMCG Products Ltd.</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>SHREEKARNI</t>
+          <t>SHANTHALA</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12402,17 +12435,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Shree OSFM E-Mobility Ltd.</t>
+          <t>Sharp Chucks and Machines Ltd.</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>SHREEOSFM</t>
+          <t>SCML</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12422,17 +12455,17 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Shree Tirupati Balajee FIBC Ltd.</t>
+          <t>Sheel Biotech Ltd.</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>TIRUPATI</t>
+          <t>SHEEL</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12442,12 +12475,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Shreeji Global FMCG Ltd.</t>
+          <t>Sheetal Universal Ltd.</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SHETHJI</t>
+          <t>SHEETAL</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -12462,17 +12495,17 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Shri Ahimsa Naturals Ltd.</t>
+          <t>Shera Energy Ltd.</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>SHRIAHIMSA</t>
+          <t>SHERA</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12482,17 +12515,17 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Shri Hare-Krishna Sponge Iron Ltd.</t>
+          <t>Shigan Quantum Technologies Ltd.</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>SHKSIL</t>
+          <t>SHIGAN</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -12502,12 +12535,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Shri Kanha Stainless Ltd.</t>
+          <t>Shivalic Power Control Ltd.</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>SHRIKANHA</t>
+          <t>SPCL</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -12522,17 +12555,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Shri Techtex Ltd.</t>
+          <t>Shivashrit Foods Ltd.</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>SHRITECH</t>
+          <t>SHIVASHRIT</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12542,17 +12575,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Shubhlaxmi Jewel Art Ltd.</t>
+          <t>Shree Karni Fabcom Ltd.</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>SHUBHLAXMI</t>
+          <t>SHREEKARNI</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -12562,17 +12595,17 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Shubhshree Biofuels Energy Ltd.</t>
+          <t>Shree OSFM E-Mobility Ltd.</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>SHUBHSHREE</t>
+          <t>SHREEOSFM</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12582,17 +12615,17 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Shyam Dhani Industries Ltd.</t>
+          <t>Shree Tirupati Balajee FIBC Ltd.</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>SHYAMDHANI</t>
+          <t>TIRUPATI</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12602,12 +12635,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Siddhi Cotspin Ltd.</t>
+          <t>Shreedhar Spinners Ltd.</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>SIDDHICOTS</t>
+          <t>SHREEDHAR</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -12622,17 +12655,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Siddhika Coatings Ltd.</t>
+          <t>Shreeji Global FMCG Ltd.</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>SIDDHIKA</t>
+          <t>SHETHJI</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12642,17 +12675,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Signoria Creation Ltd.</t>
+          <t>Shri Ahimsa Naturals Ltd.</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>SIGNORIA</t>
+          <t>SHRIAHIMSA</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12662,17 +12695,17 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Silkflex Polymers (India) Ltd.</t>
+          <t>Shri Hare-Krishna Sponge Iron Ltd.</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>SILKFLEX</t>
+          <t>SHKSIL</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -12682,17 +12715,17 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Silky Overseas Ltd.</t>
+          <t>Shri Kanha Stainless Ltd.</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>SILKY</t>
+          <t>SHRIKANHA</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12702,17 +12735,17 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Simca Advertising Ltd.</t>
+          <t>Shri Techtex Ltd.</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>SIMCA</t>
+          <t>SHRITECH</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12722,17 +12755,17 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>SKP Bearing Industries Ltd.</t>
+          <t>Shubhlaxmi Jewel Art Ltd.</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>SKP</t>
+          <t>SHUBHLAXMI</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -12742,17 +12775,17 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Slone Infosystems Ltd.</t>
+          <t>Shubhshree Biofuels Energy Ltd.</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>SLONE</t>
+          <t>SHUBHSHREE</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12762,17 +12795,17 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Smarten Power Systems Ltd.</t>
+          <t>Shyam Dhani Industries Ltd.</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>SMARTEN</t>
+          <t>SHYAMDHANI</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12782,17 +12815,17 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>SMVD Poly Pack Ltd.</t>
+          <t>Siddhi Cotspin Ltd.</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>SMVD</t>
+          <t>SIDDHICOTS</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -12802,17 +12835,17 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Snehaa Organics Ltd.</t>
+          <t>Siddhika Coatings Ltd.</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SNEHAA</t>
+          <t>SIDDHIKA</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -12822,17 +12855,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Solve Plastic Products Ltd.</t>
+          <t>Signoria Creation Ltd.</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>BALCO</t>
+          <t>SIGNORIA</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12875,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Sona Machinery Ltd.</t>
+          <t>Silkflex Polymers (India) Ltd.</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>SONAMAC</t>
+          <t>SILKFLEX</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -12862,17 +12895,17 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Sonu Infratech Ltd.</t>
+          <t>Silky Overseas Ltd.</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>SONUINFRA</t>
+          <t>SILKY</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -12882,17 +12915,17 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Sotac Pharmaceuticals Ltd.</t>
+          <t>Simca Advertising Ltd.</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>SOTAC</t>
+          <t>SIMCA</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -12902,12 +12935,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Sp Refractories Ltd.</t>
+          <t>SKP Bearing Industries Ltd.</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>SPRL</t>
+          <t>SKP</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -12922,17 +12955,17 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Speb Adhesives Ltd.</t>
+          <t>Slone Infosystems Ltd.</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>SPEB</t>
+          <t>SLONE</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -12942,17 +12975,17 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Spectrum Talent Management Ltd.</t>
+          <t>Smarten Power Systems Ltd.</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>SPECTSTM</t>
+          <t>SMARTEN</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12962,12 +12995,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>SPP Polymer Ltd.</t>
+          <t>SMVD Poly Pack Ltd.</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>SPPPOLY</t>
+          <t>SMVD</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -12982,17 +13015,17 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Spunweb Nonwoven Ltd.</t>
+          <t>Snehaa Organics Ltd.</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>SPUNWEB</t>
+          <t>SNEHAA</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -13002,17 +13035,17 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Srinibas Pradhan Constructions Ltd.</t>
+          <t>Solve Plastic Products Ltd.</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>SPCON</t>
+          <t>BALCO</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13022,17 +13055,17 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Srivari Spices And Foods Ltd.</t>
+          <t>Sona Machinery Ltd.</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>SSFL</t>
+          <t>SONAMAC</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13042,17 +13075,17 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Srivasavi Adhesive Tapes Ltd.</t>
+          <t>Sonu Infratech Ltd.</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>SRIVASAVI</t>
+          <t>SONUINFRA</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -13062,17 +13095,17 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Striders Impex Ltd.</t>
+          <t>Sotac Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>STRIDERS</t>
+          <t>SOTAC</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -13082,17 +13115,17 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Studio LSD Ltd.</t>
+          <t>Sp Refractories Ltd.</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>STUDIOLSD</t>
+          <t>SPRL</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13102,17 +13135,17 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Suba Hotels Ltd.</t>
+          <t>Speb Adhesives Ltd.</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>SUBAHOTELS</t>
+          <t>SPEB</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -13122,17 +13155,17 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Sundrex Oil Company Ltd.</t>
+          <t>Spectrum Talent Management Ltd.</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>SOCL</t>
+          <t>SPECTSTM</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -13142,12 +13175,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Sungarner Energies Ltd.</t>
+          <t>SPP Polymer Ltd.</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>SPPPOLY</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -13162,17 +13195,17 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Sunlite Recycling Industries Ltd.</t>
+          <t>Spunweb Nonwoven Ltd.</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>SUNLITE</t>
+          <t>SPUNWEB</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -13182,17 +13215,17 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Sunrest Lifescience Ltd.</t>
+          <t>Srinibas Pradhan Constructions Ltd.</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>SUNREST</t>
+          <t>SPCON</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -13202,17 +13235,17 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Suntech Infra Solutions Ltd.</t>
+          <t>Srivari Spices And Foods Ltd.</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>SUNTECH</t>
+          <t>SSFL</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -13222,17 +13255,17 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Supreme Facility Management Ltd.</t>
+          <t>Srivasavi Adhesive Tapes Ltd.</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>SFML</t>
+          <t>SRIVASAVI</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13242,17 +13275,17 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Supreme Power Equipment Ltd.</t>
+          <t>Striders Impex Ltd.</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>SUPREMEPWR</t>
+          <t>STRIDERS</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -13262,17 +13295,17 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Surani Steel Tubes Ltd.</t>
+          <t>Studio LSD Ltd.</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>SURANI</t>
+          <t>STUDIOLSD</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -13282,17 +13315,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Swastik Pipe Ltd.</t>
+          <t>Suba Hotels Ltd.</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>SWASTIK</t>
+          <t>SUBAHOTELS</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -13302,17 +13335,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Sylvan Plyboard (India) Ltd.</t>
+          <t>Sundrex Oil Company Ltd.</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>SYLVANPLY</t>
+          <t>SOCL</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -13322,17 +13355,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Synoptics Technologies Ltd.</t>
+          <t>Sungarner Energies Ltd.</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>SYNOPTICS</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13342,17 +13375,17 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Systango Technologies Ltd.</t>
+          <t>Sunlite Recycling Industries Ltd.</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>SYSTANGO</t>
+          <t>SUNLITE</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13362,17 +13395,17 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>TAC INFOSEC Ltd.</t>
+          <t>Sunrest Lifescience Ltd.</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>TAC</t>
+          <t>SUNREST</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -13382,17 +13415,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Tankup Engineers Ltd.</t>
+          <t>Suntech Infra Solutions Ltd.</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>TANKUP</t>
+          <t>SUNTECH</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -13402,17 +13435,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Tapi Fruit Processing Ltd.</t>
+          <t>Supreme Facility Management Ltd.</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>TAPIFRUIT</t>
+          <t>SFML</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -13422,12 +13455,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Taurian MPS Ltd.</t>
+          <t>Supreme Power Equipment Ltd.</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>TAURIAN</t>
+          <t>SUPREMEPWR</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -13442,17 +13475,17 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>TBI Corn Ltd.</t>
+          <t>Surani Steel Tubes Ltd.</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>TBI</t>
+          <t>SURANI</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13462,17 +13495,17 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>TechD Cybersecurity Ltd.</t>
+          <t>Swastik Pipe Ltd.</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>TECHD</t>
+          <t>SWASTIK</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13482,17 +13515,17 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>TechEra Engineering (India) Ltd.</t>
+          <t>Sylvan Plyboard (India) Ltd.</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>TECHERA</t>
+          <t>SYLVANPLY</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -13502,17 +13535,17 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>TEERTH GOPICON Ltd.</t>
+          <t>Synoptics Technologies Ltd.</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>TGL</t>
+          <t>SYNOPTICS</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13522,17 +13555,17 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Tejas Cargo India Ltd.</t>
+          <t>Systango Technologies Ltd.</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>TEJASCARGO</t>
+          <t>SYSTANGO</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13542,17 +13575,17 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Thaai Casting Ltd.</t>
+          <t>TAC INFOSEC Ltd.</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>TCL</t>
+          <t>TAC</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13562,17 +13595,17 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Thinking Hats Entertainment Solutions Ltd.</t>
+          <t>Tankup Engineers Ltd.</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>THESL</t>
+          <t>TANKUP</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13582,17 +13615,17 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Timescan Logistics (India) Ltd.</t>
+          <t>Tapi Fruit Processing Ltd.</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>TIMESCAN</t>
+          <t>TAPIFRUIT</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -13602,17 +13635,17 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Transteel Seating Technologies Ltd.</t>
+          <t>Taurian MPS Ltd.</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>TRANSTEEL</t>
+          <t>TAURIAN</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13622,17 +13655,17 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Transwind Infra Ltd.</t>
+          <t>TBI Corn Ltd.</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>TRANSWIND</t>
+          <t>TBI</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -13642,17 +13675,17 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Trident Techlabs Ltd.</t>
+          <t>Teamtech Formwork Solutions Ltd.</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>TECHLABS</t>
+          <t>TEAMTECH</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -13662,12 +13695,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Tridhya Tech Ltd.</t>
+          <t>TechD Cybersecurity Ltd.</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>TRIDHYA</t>
+          <t>TECHD</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -13682,12 +13715,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Trom Industries Ltd.</t>
+          <t>TechEra Engineering (India) Ltd.</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>TROM</t>
+          <t>TECHERA</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -13702,17 +13735,17 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Trust Fintech Ltd.</t>
+          <t>TEERTH GOPICON Ltd.</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>TRUST</t>
+          <t>TGL</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -13722,17 +13755,17 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>TSC India Ltd.</t>
+          <t>Teja Engineering Industries Ltd.</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>TSC</t>
+          <t>TEJA</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -13742,17 +13775,17 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Tunwal E-Motors Ltd.</t>
+          <t>Tejas Cargo India Ltd.</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>TUNWAL</t>
+          <t>TEJASCARGO</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -13762,12 +13795,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Ultra Wiring Connectivity System Ltd.</t>
+          <t>Thaai Casting Ltd.</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>UWCSL</t>
+          <t>TCL</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -13782,17 +13815,17 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Uma Converter Ltd.</t>
+          <t>Thinking Hats Entertainment Solutions Ltd.</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>UMA</t>
+          <t>THESL</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -13802,17 +13835,17 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Unihealth Hospitals Ltd.</t>
+          <t>Timescan Logistics (India) Ltd.</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>UNIHEALTH</t>
+          <t>TIMESCAN</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -13822,17 +13855,17 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Unilex Colours and Chemicals Ltd.</t>
+          <t>Transteel Seating Technologies Ltd.</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>UNILEX</t>
+          <t>TRANSTEEL</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -13842,17 +13875,17 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>United Heat Transfer Ltd.</t>
+          <t>Transwind Infra Ltd.</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>UHTL</t>
+          <t>TRANSWIND</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -13862,17 +13895,17 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Upsurge Seeds of Agriculture Ltd.</t>
+          <t>Trident Techlabs Ltd.</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>USASEEDS</t>
+          <t>TECHLABS</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13882,17 +13915,17 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Urban Enviro Waste Management Ltd.</t>
+          <t>Tridhya Tech Ltd.</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>URBAN</t>
+          <t>TRIDHYA</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13902,17 +13935,17 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Usha Financial Services Ltd.</t>
+          <t>Trom Industries Ltd.</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>USHAFIN</t>
+          <t>TROM</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13922,17 +13955,17 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Ushanti Colour Chem Ltd.</t>
+          <t>Trust Fintech Ltd.</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>UCL</t>
+          <t>TRUST</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13942,17 +13975,17 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Utssav CZ Gold Jewels Ltd.</t>
+          <t>TSC India Ltd.</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>UTSSAV</t>
+          <t>TSC</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -13962,17 +13995,17 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>V Marc India Ltd.</t>
+          <t>Tunwal E-Motors Ltd.</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>VMARCIND</t>
+          <t>TUNWAL</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -13982,17 +14015,17 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>V R Infraspace Ltd.</t>
+          <t>Ultra Wiring Connectivity System Ltd.</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>VR</t>
+          <t>UWCSL</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -14002,17 +14035,17 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>V.L.Infraprojects Ltd.</t>
+          <t>Uma Converter Ltd.</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>VLINFRA</t>
+          <t>UMA</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14022,17 +14055,17 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>VADIVARHE SPECIALITY CHEMICALS Ltd.</t>
+          <t>Unihealth Hospitals Ltd.</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>VSCL</t>
+          <t>UNIHEALTH</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -14042,17 +14075,17 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Vaidya Sane Ayurved Laboratories Ltd.</t>
+          <t>Unilex Colours and Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>MADHAVBAUG</t>
+          <t>UNILEX</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -14062,17 +14095,17 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Value 360 Communications Ltd.</t>
+          <t>United Heat Transfer Ltd.</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>VALUE360</t>
+          <t>UHTL</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14082,17 +14115,17 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Vasa Denticity Ltd.</t>
+          <t>Upsurge Seeds of Agriculture Ltd.</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>DENTALKART</t>
+          <t>USASEEDS</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -14102,17 +14135,17 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Vdeal System Ltd.</t>
+          <t>Urban Enviro Waste Management Ltd.</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>VDEAL</t>
+          <t>URBAN</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -14122,17 +14155,17 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Veekayem Fashion and Apparels Ltd.</t>
+          <t>Usha Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>VEEKAYEM</t>
+          <t>USHAFIN</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -14142,17 +14175,17 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Vels Film International Ltd.</t>
+          <t>Ushanti Colour Chem Ltd.</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>VELS</t>
+          <t>UCL</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -14162,17 +14195,17 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Veritaas Advertising Ltd.</t>
+          <t>Utkal Speciality Industries India Ltd.</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>VERITAAS</t>
+          <t>UTKAL</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Forest Materials</t>
         </is>
       </c>
     </row>
@@ -14182,17 +14215,17 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Vertexplus Technologies Ltd.</t>
+          <t>Utssav CZ Gold Jewels Ltd.</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>VERTEXPLUS</t>
+          <t>UTSSAV</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -14202,17 +14235,17 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Viaz Tyres Ltd.</t>
+          <t>V Marc India Ltd.</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>VIAZ</t>
+          <t>VMARCIND</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14222,17 +14255,17 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Victory Electric Vehicles International Ltd.</t>
+          <t>V R Infraspace Ltd.</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>VICTORYEV</t>
+          <t>VR</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -14242,17 +14275,17 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Vigor Plast India Ltd.</t>
+          <t>V.L.Infraprojects Ltd.</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>VIGOR</t>
+          <t>VLINFRA</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -14262,17 +14295,17 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Vijaypd Ceutical Ltd.</t>
+          <t>VADIVARHE SPECIALITY CHEMICALS Ltd.</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>VIJAYPD</t>
+          <t>VSCL</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -14282,17 +14315,17 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Vilas Transcore Ltd.</t>
+          <t>Vaidya Sane Ayurved Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>VILAS</t>
+          <t>MADHAVBAUG</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -14302,17 +14335,17 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>VILIN BIO MED Ltd.</t>
+          <t>Value 360 Communications Ltd.</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>VILINBIO</t>
+          <t>VALUE360</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -14322,17 +14355,17 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Vinsys IT Services India Ltd.</t>
+          <t>Vasa Denticity Ltd.</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>VINSYS</t>
+          <t>DENTALKART</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -14342,12 +14375,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Vinyas Innovative Technologies Ltd.</t>
+          <t>Vdeal System Ltd.</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>VINYAS</t>
+          <t>VDEAL</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -14362,17 +14395,17 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Virtual Galaxy Infotech Ltd.</t>
+          <t>Veekayem Fashion and Apparels Ltd.</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>VGINFOTECH</t>
+          <t>VEEKAYEM</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -14382,17 +14415,17 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Visaman Global Sales Ltd.</t>
+          <t>Veritaas Advertising Ltd.</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>VISAMAN</t>
+          <t>VERITAAS</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -14402,17 +14435,17 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Visdem Technosys Ltd.</t>
+          <t>Vertexplus Technologies Ltd.</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>VISDEM</t>
+          <t>VERTEXPLUS</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -14422,17 +14455,17 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Vishnusurya Projects and Infra Ltd.</t>
+          <t>Viaz Tyres Ltd.</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>VISHNUINFR</t>
+          <t>VIAZ</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -14442,17 +14475,17 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Vishwas Agri Seeds Ltd.</t>
+          <t>Victory Electric Vehicles International Ltd.</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>VISHWAS</t>
+          <t>VICTORYEV</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -14462,17 +14495,17 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Vision Infra Equipment Solutions Ltd.</t>
+          <t>Vigor Plast India Ltd.</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>VIESL</t>
+          <t>VIGOR</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14482,17 +14515,17 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Vivid Electromech Ltd.</t>
+          <t>Vijaypd Ceutical Ltd.</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>VIVIDEL</t>
+          <t>VIJAYPD</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -14502,17 +14535,17 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Vivo Collaboration Solutions Ltd.</t>
+          <t>Vilas Transcore Ltd.</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>VIVO</t>
+          <t>VILAS</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14522,17 +14555,17 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Voler Car Ltd.</t>
+          <t>VILIN BIO MED Ltd.</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>VOLERCAR</t>
+          <t>VILINBIO</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -14542,17 +14575,17 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Walpar Nutritions Ltd.</t>
+          <t>Vinit Mobile Ltd.</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>WALPAR</t>
+          <t>VMOBILE</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -14562,12 +14595,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Winny Immigration &amp; Education Services Ltd.</t>
+          <t>Vinsys IT Services India Ltd.</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>WINNY</t>
+          <t>VINSYS</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -14582,17 +14615,17 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Winsol Engineers Ltd.</t>
+          <t>Vinyas Innovative Technologies Ltd.</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>WINSOL</t>
+          <t>VINYAS</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14602,17 +14635,17 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Wise Travel India Ltd.</t>
+          <t>Virtual Galaxy Infotech Ltd.</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>WTICAB</t>
+          <t>VGINFOTECH</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -14622,17 +14655,17 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Wol 3D India Ltd.</t>
+          <t>Visdem Technosys Ltd.</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>WOL3D</t>
+          <t>VISDEM</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -14642,17 +14675,17 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Womancart Ltd.</t>
+          <t>Vishnusurya Projects and Infra Ltd.</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>WOMANCART</t>
+          <t>VISHNUINFR</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -14662,17 +14695,17 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Yaap Digital Ltd.</t>
+          <t>Vishwas Agri Seeds Ltd.</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>YAAP</t>
+          <t>VISHWAS</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -14682,17 +14715,17 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Yash Optics &amp; Lens Ltd.</t>
+          <t>Vision Infra Equipment Solutions Ltd.</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>YASHOPTICS</t>
+          <t>VIESL</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -14702,17 +14735,17 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Yasons Chemex Care Ltd.</t>
+          <t>Vivid Electromech Ltd.</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>YCCL</t>
+          <t>VIVIDEL</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14722,17 +14755,17 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Yudiz Solutions Ltd.</t>
+          <t>Vivo Collaboration Solutions Ltd.</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>YUDIZ</t>
+          <t>VIVO</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -14742,17 +14775,17 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Z-Tech (India) Ltd.</t>
+          <t>Voler Car Ltd.</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>ZTECH</t>
+          <t>VOLERCAR</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -14762,17 +14795,17 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Zeal Global Services Ltd.</t>
+          <t>Walpar Nutritions Ltd.</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>ZEAL</t>
+          <t>WALPAR</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -14782,15 +14815,235 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
+          <t>Winny Immigration &amp; Education Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>WINNY</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>529</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Winsol Engineers Ltd.</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>WINSOL</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>530</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Wise Travel India Ltd.</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>WTICAB</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>531</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Wol 3D India Ltd.</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>WOL3D</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>532</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Womancart Ltd.</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>WOMANCART</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>533</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Yaap Digital Ltd.</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>YAAP</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Media Entertainment &amp; Publication</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>534</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Yash Optics &amp; Lens Ltd.</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>YASHOPTICS</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>535</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Yasons Chemex Care Ltd.</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>YCCL</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>536</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Yudiz Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>YUDIZ</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>537</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Z-Tech (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>ZTECH</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>538</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Zeal Global Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>ZEAL</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>539</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
           <t>Zenith Drugs Ltd.</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr">
+      <c r="C544" t="inlineStr">
         <is>
           <t>ZENITHDRUG</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr">
+      <c r="D544" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15119.05</v>
+        <v>15215.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.97</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1328125</v>
+        <v>0.1384615384615385</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>658.2085328689595</v>
+        <v>648.0004258943782</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1368930072765195</v>
+        <v>0.1616502822178856</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.043535045711798</v>
+        <v>0.04258943781942078</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>86.71875</v>
+        <v>86.15384615384616</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>74.75720291060782</v>
+        <v>82.33005644357712</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>83.13028587318234</v>
+        <v>85.00670924076545</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>43.47073401958684</v>
+        <v>46.37866917860521</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>28612.80806176902</v>
+        <v>30053.39738015064</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.8925003926681256</v>
+        <v>0.9752414471296935</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>84.41578006528954</v>
+        <v>90.41285943225337</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>55563.18674776299</v>
+        <v>58587.57141842873</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.675044843939467</v>
+        <v>2.850632854865986</v>
       </c>
     </row>
     <row r="16">
@@ -815,7 +815,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="30" t="n">
-        <v>0.3855604153458748</v>
+        <v>0.0790931435489195</v>
       </c>
       <c r="D18" s="30" t="n">
         <v>0.6995397341765872</v>
@@ -838,10 +838,10 @@
         <v>7</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.2545961209779297</v>
+        <v>0.1016046898710225</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.6313516348216295</v>
+        <v>0.5703407899802942</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.6529708196426627</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.432145757920493</v>
+        <v>0.5395879746677013</v>
       </c>
       <c r="D20" s="30" t="n">
         <v>0.3327947040781369</v>
@@ -913,7 +913,7 @@
         <v>0.7407205559391973</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>0.4667935158060869</v>
+        <v>0.3990736235708736</v>
       </c>
       <c r="F22" s="30" t="n"/>
       <c r="G22" s="30" t="n">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
@@ -967,7 +967,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2282,6 +2282,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>15215.05</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2298,7 +2317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2398,7 +2417,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,C2)+1)/2)/COUNTIFS($D$2:$D$36,D2,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,C2)+1)/2)/COUNTIFS($D$2:$D$37,D2,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2440,7 +2459,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,C3)+1)/2)/COUNTIFS($D$2:$D$36,D3,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,C3)+1)/2)/COUNTIFS($D$2:$D$37,D3,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2482,7 +2501,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,C4)+1)/2)/COUNTIFS($D$2:$D$36,D4,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,C4)+1)/2)/COUNTIFS($D$2:$D$37,D4,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2524,7 +2543,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,C5)+1)/2)/COUNTIFS($D$2:$D$36,D5,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,C5)+1)/2)/COUNTIFS($D$2:$D$37,D5,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2569,7 +2588,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,C6)+1)/2)/COUNTIFS($D$2:$D$36,D6,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,C6)+1)/2)/COUNTIFS($D$2:$D$37,D6,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2614,7 +2633,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,C7)+1)/2)/COUNTIFS($D$2:$D$36,D7,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,C7)+1)/2)/COUNTIFS($D$2:$D$37,D7,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2659,7 +2678,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,C8)+1)/2)/COUNTIFS($D$2:$D$36,D8,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,C8)+1)/2)/COUNTIFS($D$2:$D$37,D8,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2704,7 +2723,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,C9)+1)/2)/COUNTIFS($D$2:$D$36,D9,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,C9)+1)/2)/COUNTIFS($D$2:$D$37,D9,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2749,7 +2768,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,C10)+1)/2)/COUNTIFS($D$2:$D$36,D10,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,C10)+1)/2)/COUNTIFS($D$2:$D$37,D10,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2794,7 +2813,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,C11)+1)/2)/COUNTIFS($D$2:$D$36,D11,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,C11)+1)/2)/COUNTIFS($D$2:$D$37,D11,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2839,7 +2858,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,C12)+1)/2)/COUNTIFS($D$2:$D$36,D12,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,C12)+1)/2)/COUNTIFS($D$2:$D$37,D12,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2884,7 +2903,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,C13)+1)/2)/COUNTIFS($D$2:$D$36,D13,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,C13)+1)/2)/COUNTIFS($D$2:$D$37,D13,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2929,7 +2948,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,C14)+1)/2)/COUNTIFS($D$2:$D$36,D14,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,C14)+1)/2)/COUNTIFS($D$2:$D$37,D14,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2972,7 +2991,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,C15)+1)/2)/COUNTIFS($D$2:$D$36,D15,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,C15)+1)/2)/COUNTIFS($D$2:$D$37,D15,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3017,7 +3036,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,C16)+1)/2)/COUNTIFS($D$2:$D$36,D16,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,C16)+1)/2)/COUNTIFS($D$2:$D$37,D16,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3062,7 +3081,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,C17)+1)/2)/COUNTIFS($D$2:$D$36,D17,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,C17)+1)/2)/COUNTIFS($D$2:$D$37,D17,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3077,7 +3096,10 @@
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="30" t="n"/>
+      <c r="K17" s="30">
+        <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
@@ -3104,7 +3126,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,C18)+1)/2)/COUNTIFS($D$2:$D$36,D18,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,C18)+1)/2)/COUNTIFS($D$2:$D$37,D18,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3146,7 +3168,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,C19)+1)/2)/COUNTIFS($D$2:$D$36,D19,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,C19)+1)/2)/COUNTIFS($D$2:$D$37,D19,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3188,7 +3210,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,C20)+1)/2)/COUNTIFS($D$2:$D$36,D20,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,C20)+1)/2)/COUNTIFS($D$2:$D$37,D20,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3230,7 +3252,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,C21)+1)/2)/COUNTIFS($D$2:$D$36,D21,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,C21)+1)/2)/COUNTIFS($D$2:$D$37,D21,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3272,7 +3294,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,C22)+1)/2)/COUNTIFS($D$2:$D$36,D22,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,C22)+1)/2)/COUNTIFS($D$2:$D$37,D22,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3314,7 +3336,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,C23)+1)/2)/COUNTIFS($D$2:$D$36,D23,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,C23)+1)/2)/COUNTIFS($D$2:$D$37,D23,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3356,7 +3378,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,C24)+1)/2)/COUNTIFS($D$2:$D$36,D24,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,C24)+1)/2)/COUNTIFS($D$2:$D$37,D24,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3398,7 +3420,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,C25)+1)/2)/COUNTIFS($D$2:$D$36,D25,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,C25)+1)/2)/COUNTIFS($D$2:$D$37,D25,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3409,7 +3431,10 @@
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="30" t="n"/>
+      <c r="J25" s="30">
+        <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K25" s="30" t="n"/>
       <c r="L25" s="30" t="n"/>
     </row>
@@ -3437,7 +3462,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,C26)+1)/2)/COUNTIFS($D$2:$D$36,D26,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,C26)+1)/2)/COUNTIFS($D$2:$D$37,D26,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3476,7 +3501,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,C27)+1)/2)/COUNTIFS($D$2:$D$36,D27,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,C27)+1)/2)/COUNTIFS($D$2:$D$37,D27,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3515,7 +3540,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,C28)+1)/2)/COUNTIFS($D$2:$D$36,D28,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,C28)+1)/2)/COUNTIFS($D$2:$D$37,D28,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3554,7 +3579,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,C29)+1)/2)/COUNTIFS($D$2:$D$36,D29,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,C29)+1)/2)/COUNTIFS($D$2:$D$37,D29,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3593,7 +3618,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,C30)+1)/2)/COUNTIFS($D$2:$D$36,D30,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,C30)+1)/2)/COUNTIFS($D$2:$D$37,D30,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3632,7 +3657,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,C31)+1)/2)/COUNTIFS($D$2:$D$36,D31,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,C31)+1)/2)/COUNTIFS($D$2:$D$37,D31,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3671,7 +3696,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,C32)+1)/2)/COUNTIFS($D$2:$D$36,D32,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,C32)+1)/2)/COUNTIFS($D$2:$D$37,D32,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3710,14 +3735,17 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,C33)+1)/2)/COUNTIFS($D$2:$D$36,D33,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,C33)+1)/2)/COUNTIFS($D$2:$D$37,D33,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="30" t="n"/>
+      <c r="I33" s="30">
+        <f>IFERROR(B37/B33-1,"")</f>
+        <v/>
+      </c>
       <c r="J33" s="30" t="n"/>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
@@ -3746,7 +3774,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,C34)+1)/2)/COUNTIFS($D$2:$D$36,D34,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,C34)+1)/2)/COUNTIFS($D$2:$D$37,D34,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3782,7 +3810,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,C35)+1)/2)/COUNTIFS($D$2:$D$36,D35,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,C35)+1)/2)/COUNTIFS($D$2:$D$37,D35,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3818,7 +3846,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0",$C$2:$C$36,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,C36)+1)/2)/COUNTIFS($D$2:$D$36,D36,$C$2:$C$36,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,C36)+1)/2)/COUNTIFS($D$2:$D$37,D36,$C$2:$C$37,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3829,6 +3857,42 @@
       <c r="J36" s="30" t="n"/>
       <c r="K36" s="30" t="n"/>
       <c r="L36" s="30" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B37" s="24" t="n">
+        <v>15215.05</v>
+      </c>
+      <c r="C37" s="25" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E37" s="33">
+        <f>IFERROR(B37/C37,"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="30">
+        <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="30">
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0",$C$2:$C$37,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,C37)+1)/2)/COUNTIFS($D$2:$D$37,D37,$C$2:$C$37,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I37" s="30" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3843,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3851,7 +3915,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4165,6 +4229,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>15215.05</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.138461538462</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.161650282218</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4205,7 +4302,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15215.05</v>
+        <v>14993.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.48</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1384615384615385</v>
+        <v>0.1307692307692308</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>648.0004258943782</v>
+        <v>647.9407951598963</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1616502822178856</v>
+        <v>0.1613319069595434</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04258943781942078</v>
+        <v>0.0432152117545376</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>86.15384615384616</v>
+        <v>86.92307692307692</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.33005644357712</v>
+        <v>82.26638139190867</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.00670924076545</v>
+        <v>85.52606826372644</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.37866917860521</v>
+        <v>46.34059513628184</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30053.39738015064</v>
+        <v>30025.96206078528</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.9752414471296935</v>
+        <v>1.002618631645715</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.41285943225337</v>
+        <v>90.356671012969</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>58587.57141842873</v>
+        <v>58545.77326414429</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.850632854865986</v>
+        <v>2.904782671260545</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4262,6 +4262,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>14993.35</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.16133190696</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4302,7 +4335,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14993.35</v>
+        <v>15041.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.14</v>
+        <v>23.21</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>647.9407951598963</v>
+        <v>648.0654890133563</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1613319069595434</v>
+        <v>0.1615668278774776</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0432152117545376</v>
+        <v>0.04308487720809995</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.26638139190867</v>
+        <v>82.31336557549551</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.52606826372644</v>
+        <v>85.54016351880249</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.34059513628184</v>
+        <v>46.36868899325627</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30025.96206078528</v>
+        <v>30049.94710732286</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.002618631645715</v>
+        <v>0.9977892715750225</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.356671012969</v>
+        <v>90.38987753755082</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>58545.77326414429</v>
+        <v>58578.56018823027</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.904782671260545</v>
+        <v>2.89443677456057</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4295,6 +4295,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>15041.6</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.161566827877</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4335,7 +4368,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15041.6</v>
+        <v>15196.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.21</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>648.0654890133563</v>
+        <v>651.3823403343335</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1615668278774776</v>
+        <v>0.1676388373359348</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04308487720809995</v>
+        <v>0.04286326618088299</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.31336557549551</v>
+        <v>83.52776746718695</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.54016351880249</v>
+        <v>85.90448408630992</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.36868899325627</v>
+        <v>47.09483193009393</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30049.94710732286</v>
+        <v>30676.74184027669</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.9977892715750225</v>
+        <v>1.018638316763564</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.38987753755082</v>
+        <v>92.06200485081925</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>58578.56018823027</v>
+        <v>59967.56417559741</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.89443677456057</v>
+        <v>2.946078219066407</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4328,6 +4328,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>15196.75</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.167638837336</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4368,7 +4401,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15196.75</v>
+        <v>15240.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.33</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>651.3823403343335</v>
+        <v>651.8627031650984</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1676388373359348</v>
+        <v>0.1683760861889629</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04286326618088299</v>
+        <v>0.0427715996578272</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.52776746718695</v>
+        <v>83.67521723779259</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.90448408630992</v>
+        <v>85.94871901749161</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>47.09483193009393</v>
+        <v>47.18299846721493</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30676.74184027669</v>
+        <v>30756.83692427342</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.018638316763564</v>
+        <v>1.018092321095592</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>92.06200485081925</v>
+        <v>92.26503054639144</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59967.56417559741</v>
+        <v>60144.1322195811</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.946078219066407</v>
+        <v>2.946322948947453</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4361,6 +4361,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>15240.55</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.168376086189</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4401,7 +4434,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15240.55</v>
+        <v>15016.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.38</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>651.8627031650984</v>
+        <v>652.6119078661451</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1683760861889629</v>
+        <v>0.1627303777245563</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0427715996578272</v>
+        <v>0.0434593654932638</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.67521723779259</v>
+        <v>82.54607554491128</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.94871901749161</v>
+        <v>85.60997650962722</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>47.18299846721493</v>
+        <v>46.50783625725436</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30756.83692427342</v>
+        <v>30351.56775057305</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.018092321095592</v>
+        <v>1.021201054204883</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>92.26503054639144</v>
+        <v>90.71029921886753</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>60144.1322195811</v>
+        <v>59198.62143633403</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.946322948947453</v>
+        <v>2.942212047756085</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4394,6 +4394,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>15016.6</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.162730377725</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4434,7 +4467,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15016.6</v>
+        <v>15027.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.01</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.6119078661451</v>
+        <v>652.7997393570809</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1627303777245563</v>
+        <v>0.162817304257445</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0434593654932638</v>
+        <v>0.04344048653344917</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.54607554491128</v>
+        <v>82.563460851489</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.60997650962722</v>
+        <v>85.61519210160054</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.50783625725436</v>
+        <v>46.51823167714177</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30351.56775057305</v>
+        <v>30367.08951419045</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.021201054204883</v>
+        <v>1.020774616730746</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.71029921886753</v>
+        <v>90.73423729585593</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59198.62143633403</v>
+        <v>59231.28645749828</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.942212047756085</v>
+        <v>2.941539413373412</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4427,6 +4427,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>15027.45</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.162817304257</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4467,7 +4500,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15027.45</v>
+        <v>15027</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.7997393570809</v>
+        <v>652.7801911381407</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.162817304257445</v>
+        <v>0.163363839895885</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.563460851489</v>
+        <v>82.672767979177</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.61519210160054</v>
+        <v>85.64798423990693</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.51823167714177</v>
+        <v>46.58359109337758</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30367.08951419045</v>
+        <v>30408.84549783601</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.020774616730746</v>
+        <v>1.023613861571572</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.73423729585593</v>
+        <v>90.88474384149994</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59231.28645749828</v>
+        <v>59327.76045639528</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.941539413373412</v>
+        <v>2.948077490942655</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4460,6 +4460,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>15027</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.163363839896</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4500,7 +4533,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15027</v>
+        <v>15048.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.02</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.7801911381407</v>
+        <v>652.5672159583695</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.163363839895885</v>
+        <v>0.1631942460936362</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04344048653344917</v>
+        <v>0.04336513443191674</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.672767979177</v>
+        <v>82.63884921872724</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.64798423990693</v>
+        <v>85.63780861177202</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.58359109337758</v>
+        <v>46.56330961284354</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30408.84549783601</v>
+        <v>30385.68931986089</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.023613861571572</v>
+        <v>1.019224180955921</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.88474384149994</v>
+        <v>90.83804061568293</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59327.76045639528</v>
+        <v>59277.9272676895</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.948077490942655</v>
+        <v>2.939203842831003</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4493,6 +4493,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>15048.2</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.163194246094</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4533,7 +4566,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15048.2</v>
+        <v>15172.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.06</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.5672159583695</v>
+        <v>652.5698924731183</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1631942460936362</v>
+        <v>0.1628327196176111</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04336513443191674</v>
+        <v>0.04301075268817205</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.63884921872724</v>
+        <v>82.56654392352223</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.63780861177202</v>
+        <v>85.61611702321051</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.56330961284354</v>
+        <v>46.52007517804208</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30385.68931986089</v>
+        <v>30357.6004567763</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.019224180955921</v>
+        <v>1.000863448517939</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.83804061568293</v>
+        <v>90.73848242178239</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59277.9272676895</v>
+        <v>59213.20171715647</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.939203842831003</v>
+        <v>2.902730426743329</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4526,6 +4526,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>15172.25</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.162832719618</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4566,7 +4599,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15172.25</v>
+        <v>15145.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.25</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.5698924731183</v>
+        <v>652.8060344827586</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1628327196176111</v>
+        <v>0.1635159700680584</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04301075268817205</v>
+        <v>0.04310344827586207</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.56654392352223</v>
+        <v>82.70319401361168</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.61611702321051</v>
+        <v>85.65711205023734</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.52007517804208</v>
+        <v>46.60178412333899</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30357.6004567763</v>
+        <v>30421.92589337851</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.000863448517939</v>
+        <v>1.008697591523232</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.73848242178239</v>
+        <v>90.92663788297068</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59213.20171715647</v>
+        <v>59357.45790523187</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.902730426743329</v>
+        <v>2.919251632886667</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4559,6 +4559,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>15145.1</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.163515970068</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4599,7 +4632,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15145.1</v>
+        <v>15130</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.2</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.8060344827586</v>
+        <v>652.7178602243313</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1635159700680584</v>
+        <v>0.1634792879174274</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04310344827586207</v>
+        <v>0.04314063848144953</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.70319401361168</v>
+        <v>82.69585758348548</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.65711205023734</v>
+        <v>85.65491112119949</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.60178412333899</v>
+        <v>46.59739735734811</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30421.92589337851</v>
+        <v>30414.95349511117</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.008697591523232</v>
+        <v>1.010241473569806</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.92663788297068</v>
+        <v>90.91653624752377</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59357.45790523187</v>
+        <v>59342.84699849156</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.919251632886667</v>
+        <v>2.922197422240024</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4592,6 +4592,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>15130</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.130769230769</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.163479287917</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4632,7 +4665,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>15130</v>
+        <v>14870.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.18</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1307692307692308</v>
+        <v>0.08461538461538462</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.7178602243313</v>
+        <v>652.8007023705004</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1634792879174274</v>
+        <v>0.1633174197411855</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04314063848144953</v>
+        <v>0.04389815627743635</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>86.92307692307692</v>
+        <v>91.53846153846153</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.69585758348548</v>
+        <v>82.6634839482371</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>85.65491112119949</v>
+        <v>88.87596826139419</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.59739735734811</v>
+        <v>46.5780397733916</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30414.95349511117</v>
+        <v>30406.17707911114</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.010241473569806</v>
+        <v>1.04469006906899</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.91653624752377</v>
+        <v>90.87196052666975</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59342.84699849156</v>
+        <v>59321.2796575944</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.922197422240024</v>
+        <v>2.989111524436776</v>
       </c>
     </row>
     <row r="16">
@@ -3907,13 +3907,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -4625,6 +4625,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>14870.8</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.0846153846154</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.163317419741</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4665,7 +4698,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14870.8</v>
+        <v>14448</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.78</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08461538461538462</v>
+        <v>0.06923076923076923</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.8007023705004</v>
+        <v>652.5745257452575</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1633174197411855</v>
+        <v>0.1629954774795173</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04389815627743635</v>
+        <v>0.04516711833785005</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.53846153846153</v>
+        <v>93.07692307692308</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.6634839482371</v>
+        <v>82.59909549590346</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>88.87596826139419</v>
+        <v>89.93357480261719</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.5780397733916</v>
+        <v>46.53953915823621</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30406.17707911114</v>
+        <v>30370.51769458883</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.04469006906899</v>
+        <v>1.102056872549061</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.87196052666975</v>
+        <v>90.78330314681654</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59321.2796575944</v>
+        <v>59242.87099662174</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>2.989111524436776</v>
+        <v>3.100420196333177</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4658,6 +4658,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>14448</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.0692307692308</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.16299547748</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4698,7 +4731,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14448</v>
+        <v>14329.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.14</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.5745257452575</v>
+        <v>652.8246013667426</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1629954774795173</v>
+        <v>0.16344115349864</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04516711833785005</v>
+        <v>0.04555808656036447</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.59909549590346</v>
+        <v>82.688230699728</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>89.93357480261719</v>
+        <v>89.96031536376455</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.53953915823621</v>
+        <v>46.59283691668308</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30370.51769458883</v>
+        <v>30416.95018667928</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.102056872549061</v>
+        <v>1.122680497343193</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.78330314681654</v>
+        <v>90.90603468232261</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59242.87099662174</v>
+        <v>59345.69585331854</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>3.100420196333177</v>
+        <v>3.141504996916748</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4691,6 +4691,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>14329.5</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.0692307692308</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.163441153499</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4731,7 +4764,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14329.5</v>
+        <v>13972.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.95</v>
+        <v>21.41</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06923076923076923</v>
+        <v>0.03846153846153846</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.8246013667426</v>
+        <v>652.6296123306865</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.16344115349864</v>
+        <v>0.1629724741368697</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04555808656036447</v>
+        <v>0.04670714619336758</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.07692307692308</v>
+        <v>96.15384615384616</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.688230699728</v>
+        <v>82.59449482737394</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>89.96031536376455</v>
+        <v>92.08604075590449</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.59283691668308</v>
+        <v>46.53678822135091</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30416.95018667928</v>
+        <v>30371.28605601551</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.122680497343193</v>
+        <v>1.173600570824424</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.90603468232261</v>
+        <v>90.77696842059441</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59345.69585331854</v>
+        <v>59243.73770888751</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>3.141504996916748</v>
+        <v>3.239933135011416</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4724,6 +4724,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>13972.8</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.0384615384615</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.162972474137</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4764,7 +4797,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>13972.8</v>
+        <v>14089.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.41</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03846153846153846</v>
+        <v>0.05384615384615385</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.6296123306865</v>
+        <v>652.5961093098656</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1629724741368697</v>
+        <v>0.1632067401106823</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04670714619336758</v>
+        <v>0.04631773969430292</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.15384615384616</v>
+        <v>94.61538461538461</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.59449482737394</v>
+        <v>82.64134802213646</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.08604075590449</v>
+        <v>91.02317363741017</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.53678822135091</v>
+        <v>46.56480375449348</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30371.28605601551</v>
+        <v>30388.00976095986</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.173600570824424</v>
+        <v>1.156776459216928</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.77696842059441</v>
+        <v>90.8414812537943</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59243.73770888751</v>
+        <v>59282.79723017125</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>3.239933135011416</v>
+        <v>3.207572082158142</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4757,6 +4757,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>14089.55</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.0538461538462</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.163206740111</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4797,7 +4830,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14089.55</v>
+        <v>14293.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.59</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05384615384615385</v>
+        <v>0.06923076923076923</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.5961093098656</v>
+        <v>652.0757299270073</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1632067401106823</v>
+        <v>0.1620023683839515</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04631773969430292</v>
+        <v>0.04562043795620438</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.61538461538461</v>
+        <v>93.07692307692308</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.64134802213646</v>
+        <v>82.40047367679031</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.02317363741017</v>
+        <v>89.87398825688324</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.56480375449348</v>
+        <v>46.42077466022478</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30388.00976095986</v>
+        <v>30269.86052034319</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.156776459216928</v>
+        <v>1.117736070265729</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.8414812537943</v>
+        <v>90.5098179266251</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59282.79723017125</v>
+        <v>59019.25559006459</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>3.207572082158142</v>
+        <v>3.129097533148955</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4790,6 +4790,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>14293.5</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.0692307692308</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.162002368384</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4830,7 +4863,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14293.5</v>
+        <v>14251</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.92</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>652.0757299270073</v>
+        <v>651.623228166438</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1620023683839515</v>
+        <v>0.1612697140911294</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04562043795620438</v>
+        <v>0.04572473708276177</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.40047367679031</v>
+        <v>82.25394281822589</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>89.87398825688324</v>
+        <v>89.83002899931391</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.42077466022478</v>
+        <v>46.33315757999517</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30269.86052034319</v>
+        <v>30191.76171342072</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.117736070265729</v>
+        <v>1.11857144855945</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.5098179266251</v>
+        <v>90.3550333858967</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>59019.25559006459</v>
+        <v>58877.43853600429</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>3.129097533148955</v>
+        <v>3.131460145674289</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4823,6 +4823,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>14251</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.0692307692308</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.161269714091</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4863,7 +4896,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-sme-emerge.xlsx
+++ b/docs/downloads/indices/nifty-sme-emerge.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>14408.15</v>
+        <v>14278.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.11</v>
+        <v>21.89</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>651.6576209859792</v>
+        <v>652.297852900868</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1612490306745926</v>
+        <v>0.1621462717132367</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04522840343735866</v>
+        <v>0.04568296025582458</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.24980613491853</v>
+        <v>82.42925434264734</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>89.8287879943217</v>
+        <v>89.88262245664035</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>46.33068407975927</v>
+        <v>46.43798385379781</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>30191.7433660689</v>
+        <v>30291.39716087748</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>1.095462871088162</v>
+        <v>1.121424570753669</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>90.35448876199155</v>
+        <v>90.54944643659601</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>58880.1911920438</v>
+        <v>59065.20949195373</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>3.086589270103643</v>
+        <v>3.136566762749932</v>
       </c>
     </row>
     <row r="16">
@@ -3907,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4889,6 +4889,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>14278.8</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.0692307692308</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.162146271713</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4929,7 +4962,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
